--- a/Empresas_por_Divisao_CNAE_RAIS_Capanema.xlsx
+++ b/Empresas_por_Divisao_CNAE_RAIS_Capanema.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH70"/>
+  <dimension ref="A1:AH71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -471,291 +471,179 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Estoque de empresas (matriz) ativas hoje, reconstruído por data de abertura (corte 31/12 de cada ano). Fonte: CNPJ/Receita Federal.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Seção</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Nome Seção</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Divisão</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Nome Divisão</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Emp. 2001</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Emp. 2003</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Emp. 2005</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Emp. 2007</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Emp. 2009</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>Emp. 2011</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>Emp. 2013</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>Emp. 2015</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>Emp. 2017</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>Emp. 2019</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>Emp. 2021</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>Emp. 2023</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>Emp. 2025</t>
-        </is>
-      </c>
-      <c r="R3" s="2" t="inlineStr">
-        <is>
-          <t>QL 2001</t>
-        </is>
-      </c>
-      <c r="S3" s="2" t="inlineStr">
-        <is>
-          <t>QL 2003</t>
-        </is>
-      </c>
-      <c r="T3" s="2" t="inlineStr">
-        <is>
-          <t>QL 2005</t>
-        </is>
-      </c>
-      <c r="U3" s="2" t="inlineStr">
-        <is>
-          <t>QL 2007</t>
-        </is>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>QL 2009</t>
-        </is>
-      </c>
-      <c r="W3" s="2" t="inlineStr">
-        <is>
-          <t>QL 2011</t>
-        </is>
-      </c>
-      <c r="X3" s="2" t="inlineStr">
-        <is>
-          <t>QL 2013</t>
-        </is>
-      </c>
-      <c r="Y3" s="2" t="inlineStr">
-        <is>
-          <t>QL 2015</t>
-        </is>
-      </c>
-      <c r="Z3" s="2" t="inlineStr">
-        <is>
-          <t>QL 2017</t>
-        </is>
-      </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>QL 2019</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr">
-        <is>
-          <t>QL 2021</t>
-        </is>
-      </c>
-      <c r="AC3" s="2" t="inlineStr">
-        <is>
-          <t>QL 2023</t>
-        </is>
-      </c>
-      <c r="AD3" s="2" t="inlineStr">
-        <is>
-          <t>QL 2025</t>
-        </is>
-      </c>
-      <c r="AE3" s="2" t="inlineStr">
-        <is>
-          <t>QL Médio</t>
-        </is>
-      </c>
-      <c r="AF3" s="2" t="inlineStr">
-        <is>
-          <t>Representat. (%)</t>
-        </is>
-      </c>
-      <c r="AG3" s="2" t="inlineStr">
-        <is>
-          <t>Cresc. 5 anos (%)</t>
-        </is>
-      </c>
-      <c r="AH3" s="2" t="inlineStr">
-        <is>
-          <t>Consistência (0-12)</t>
+          <t>Estoque de empresas (matriz) ativas hoje, reconstruído por data de abertura (corte 31/12 de cada ano). QL calculado no nível de Divisão. Fonte: CNPJ/Receita Federal.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>INDÚSTRIAS DE TRANSFORMAÇÃO</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>FABRICAÇÃO DE PRODUTOS ALIMENTÍCIOS</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3</v>
-      </c>
-      <c r="K4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L4" t="n">
-        <v>15</v>
-      </c>
-      <c r="M4" t="n">
-        <v>21</v>
-      </c>
-      <c r="N4" t="n">
-        <v>30</v>
-      </c>
-      <c r="O4" t="n">
-        <v>40</v>
-      </c>
-      <c r="P4" t="n">
-        <v>56</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>78</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.341037</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.300197</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0.498595</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0.409807</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.321292</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0.297041</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.49487</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.696232</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0.764838</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0.808101</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0.764812</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0.816955</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0.847598</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0.56626</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.557508</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>160</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>9/12</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Seção</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Nome Seção</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Divisão</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Nome Divisão</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Emp. 2001</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Emp. 2003</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Emp. 2005</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Emp. 2007</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Emp. 2009</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Emp. 2011</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Emp. 2013</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Emp. 2015</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Emp. 2017</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Emp. 2019</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Emp. 2021</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>Emp. 2023</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>Emp. 2025</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>QL 2001</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>QL 2003</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>QL 2005</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>QL 2007</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>QL 2009</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>QL 2011</t>
+        </is>
+      </c>
+      <c r="X4" s="2" t="inlineStr">
+        <is>
+          <t>QL 2013</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>QL 2015</t>
+        </is>
+      </c>
+      <c r="Z4" s="2" t="inlineStr">
+        <is>
+          <t>QL 2017</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
+          <t>QL 2019</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>QL 2021</t>
+        </is>
+      </c>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>QL 2023</t>
+        </is>
+      </c>
+      <c r="AD4" s="2" t="inlineStr">
+        <is>
+          <t>QL 2025</t>
+        </is>
+      </c>
+      <c r="AE4" s="2" t="inlineStr">
+        <is>
+          <t>QL Médio</t>
+        </is>
+      </c>
+      <c r="AF4" s="2" t="inlineStr">
+        <is>
+          <t>Representat. (%)</t>
+        </is>
+      </c>
+      <c r="AG4" s="2" t="inlineStr">
+        <is>
+          <t>Cresc. 5 anos (%)</t>
+        </is>
+      </c>
+      <c r="AH4" s="2" t="inlineStr">
+        <is>
+          <t>Consistência (0-12)</t>
         </is>
       </c>
     </row>
@@ -771,11 +659,11 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FABRICAÇÃO DE BEBIDAS</t>
+          <t>FABRICAÇÃO DE PRODUTOS ALIMENTÍCIOS</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -785,89 +673,89 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c r="R5" t="n">
-        <v>3.991395</v>
+        <v>0.341037</v>
       </c>
       <c r="S5" t="n">
-        <v>3.544266</v>
+        <v>0.300197</v>
       </c>
       <c r="T5" t="n">
-        <v>2.998692</v>
+        <v>0.498595</v>
       </c>
       <c r="U5" t="n">
-        <v>2.569172</v>
+        <v>0.409807</v>
       </c>
       <c r="V5" t="n">
-        <v>2.026873</v>
+        <v>0.321292</v>
       </c>
       <c r="W5" t="n">
-        <v>1.479994</v>
+        <v>0.297041</v>
       </c>
       <c r="X5" t="n">
-        <v>1.093146</v>
+        <v>0.49487</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.87029</v>
+        <v>0.696232</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.737615</v>
+        <v>0.764838</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.662594</v>
+        <v>0.808101</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.6067709999999999</v>
+        <v>0.764812</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.583643</v>
+        <v>0.816955</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.51623</v>
+        <v>0.847598</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.667745</v>
+        <v>0.56626</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.019968</v>
+        <v>1.557508</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0/12</t>
+          <t>9/12</t>
         </is>
       </c>
     </row>
@@ -883,30 +771,30 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FABRICAÇÃO DE PRODUTOS TÊXTEIS</t>
+          <t>FABRICAÇÃO DE BEBIDAS</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
@@ -915,71 +803,71 @@
         <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>3.991395</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.544266</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.998692</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.569172</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>2.026873</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.479994</v>
       </c>
       <c r="X6" t="n">
-        <v>0.927098</v>
+        <v>1.093146</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.676892</v>
+        <v>0.87029</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.967203</v>
+        <v>0.737615</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.091332</v>
+        <v>0.662594</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.024176</v>
+        <v>0.6067709999999999</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.875912</v>
+        <v>0.583643</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.766644</v>
+        <v>0.51623</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.486866</v>
+        <v>1.667745</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.159744</v>
+        <v>0.019968</v>
       </c>
       <c r="AG6" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>6/12</t>
+          <t>0/12</t>
         </is>
       </c>
     </row>
@@ -995,11 +883,11 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CONFECÇÃO DE ARTIGOS DO VESTUÁRIO E ACESSÓRIOS</t>
+          <t>FABRICAÇÃO DE PRODUTOS TÊXTEIS</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1009,37 +897,37 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4</v>
+      </c>
+      <c r="O7" t="n">
         <v>6</v>
       </c>
-      <c r="K7" t="n">
-        <v>9</v>
-      </c>
-      <c r="L7" t="n">
-        <v>15</v>
-      </c>
-      <c r="M7" t="n">
-        <v>17</v>
-      </c>
-      <c r="N7" t="n">
-        <v>25</v>
-      </c>
-      <c r="O7" t="n">
-        <v>35</v>
-      </c>
       <c r="P7" t="n">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="Q7" t="n">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1048,50 +936,50 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.437729</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.13861</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>0.898708</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.4887</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.160505</v>
+        <v>0.927098</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.338908</v>
+        <v>0.676892</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.192512</v>
+        <v>0.967203</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.334723</v>
+        <v>1.091332</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.458333</v>
+        <v>1.024176</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.326683</v>
+        <v>0.875912</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.373499</v>
+        <v>0.766644</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.088378</v>
+        <v>0.486866</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.9784350000000001</v>
+        <v>0.159744</v>
       </c>
       <c r="AG7" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>9/12</t>
+          <t>6/12</t>
         </is>
       </c>
     </row>
@@ -1107,51 +995,51 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>14</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CONFECÇÃO DE ARTIGOS DO VESTUÁRIO E ACESSÓRIOS</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>6</v>
+      </c>
+      <c r="K8" t="n">
+        <v>9</v>
+      </c>
+      <c r="L8" t="n">
         <v>15</v>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>PREPARAÇÃO DE COUROS E FABRICAÇÃO DE ARTEFATOS DE COURO, ARTIGOS PARA VIAGEM E CALÇADOS</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1160,50 +1048,50 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.437729</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.13861</v>
       </c>
       <c r="V8" t="n">
-        <v>10.584782</v>
+        <v>0.898708</v>
       </c>
       <c r="W8" t="n">
-        <v>3.124431</v>
+        <v>1.4887</v>
       </c>
       <c r="X8" t="n">
-        <v>1.927389</v>
+        <v>1.160505</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.32917</v>
+        <v>1.338908</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.936203</v>
+        <v>1.192512</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.7000999999999999</v>
+        <v>1.334723</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.125604</v>
+        <v>1.458333</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.801079</v>
+        <v>1.326683</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.051232</v>
+        <v>1.373499</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.659999</v>
+        <v>1.088378</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.079872</v>
+        <v>0.9784350000000001</v>
       </c>
       <c r="AG8" t="n">
-        <v>300</v>
+        <v>96</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>9/12</t>
         </is>
       </c>
     </row>
@@ -1219,11 +1107,11 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FABRICAÇÃO DE PRODUTOS DE MADEIRA</t>
+          <t>PREPARAÇÃO DE COUROS E FABRICAÇÃO DE ARTEFATOS DE COURO, ARTIGOS PARA VIAGEM E CALÇADOS</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1239,32 +1127,32 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>1</v>
       </c>
       <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
         <v>2</v>
       </c>
-      <c r="M9" t="n">
+      <c r="P9" t="n">
         <v>2</v>
       </c>
-      <c r="N9" t="n">
-        <v>2</v>
-      </c>
-      <c r="O9" t="n">
+      <c r="Q9" t="n">
         <v>4</v>
       </c>
-      <c r="P9" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>7</v>
-      </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
@@ -1278,44 +1166,44 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>10.584782</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>3.124431</v>
       </c>
       <c r="X9" t="n">
-        <v>0.162396</v>
+        <v>1.927389</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.279024</v>
+        <v>1.32917</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.23864</v>
+        <v>0.936203</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.195291</v>
+        <v>0.7000999999999999</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.299294</v>
+        <v>1.125604</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.255145</v>
+        <v>0.801079</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.375905</v>
+        <v>1.051232</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.1389</v>
+        <v>1.659999</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.139776</v>
+        <v>0.079872</v>
       </c>
       <c r="AG9" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>3/12</t>
         </is>
       </c>
     </row>
@@ -1331,11 +1219,11 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FABRICAÇÃO DE CELULOSE, PAPEL E PRODUTOS DE PAPEL</t>
+          <t>FABRICAÇÃO DE PRODUTOS DE MADEIRA</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1357,25 +1245,25 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1396,40 +1284,38 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>0.162396</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>0.279024</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>0.23864</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>0.195291</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.877589</v>
+        <v>0.299294</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.575423</v>
+        <v>0.255145</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.981071</v>
+        <v>0.375905</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.187237</v>
+        <v>0.1389</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.09984</v>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.139776</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>250</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>4/12</t>
         </is>
       </c>
     </row>
@@ -1445,103 +1331,105 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>IMPRESSÃO E REPRODUÇÃO DE GRAVAÇÕES</t>
+          <t>FABRICAÇÃO DE CELULOSE, PAPEL E PRODUTOS DE PAPEL</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
         <v>2</v>
       </c>
-      <c r="H11" t="n">
+      <c r="P11" t="n">
         <v>2</v>
       </c>
-      <c r="I11" t="n">
-        <v>3</v>
-      </c>
-      <c r="J11" t="n">
-        <v>4</v>
-      </c>
-      <c r="K11" t="n">
+      <c r="Q11" t="n">
         <v>5</v>
       </c>
-      <c r="L11" t="n">
-        <v>7</v>
-      </c>
-      <c r="M11" t="n">
-        <v>9</v>
-      </c>
-      <c r="N11" t="n">
-        <v>12</v>
-      </c>
-      <c r="O11" t="n">
-        <v>12</v>
-      </c>
-      <c r="P11" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>21</v>
-      </c>
       <c r="R11" t="n">
-        <v>1.364148</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.220803</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>1.999128</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.683995</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>2.041351</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.519994</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.158873</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.288994</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.322364</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.264953</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.92186</v>
+        <v>0.877589</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.023634</v>
+        <v>0.575423</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.048509</v>
+        <v>0.981071</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.373739</v>
+        <v>0.187237</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.419329</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>75</v>
+        <v>0.09984</v>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>9/12</t>
+          <t>2/12</t>
         </is>
       </c>
     </row>
@@ -1557,105 +1445,103 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>FABRICAÇÃO DE PRODUTOS QUÍMICOS</t>
+          <t>IMPRESSÃO E REPRODUÇÃO DE GRAVAÇÕES</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.364148</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.220803</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.999128</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.683995</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>2.041351</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.519994</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.158873</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.288994</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.322364</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.264953</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>0.92186</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.023634</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.048509</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.373739</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.419329</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>75</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0/12</t>
+          <t>9/12</t>
         </is>
       </c>
     </row>
@@ -1671,11 +1557,11 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>FABRICAÇÃO DE PRODUTOS FARMOQUÍMICOS E FARMACÊUTICOS</t>
+          <t>FABRICAÇÃO DE PRODUTOS QUÍMICOS</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1717,30 +1603,20 @@
       <c r="Q13" t="n">
         <v>0</v>
       </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -1795,11 +1671,11 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>FABRICAÇÃO DE PRODUTOS DE BORRACHA E DE MATERIAL PLÁSTICO</t>
+          <t>FABRICAÇÃO DE PRODUTOS FARMOQUÍMICOS E FARMACÊUTICOS</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1815,83 +1691,95 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.905261</v>
+        <v>0</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W14" t="n">
-        <v>3.012845</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.362606</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.00286</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.553699</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.257806</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.056689</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.276719</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.075124</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.192585</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.059904</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>50</v>
+        <v>0</v>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>0/12</t>
         </is>
       </c>
     </row>
@@ -1907,33 +1795,33 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>FABRICAÇÃO DE PRODUTOS DE MINERAIS NÃO-METÁLICOS</t>
+          <t>FABRICAÇÃO DE PRODUTOS DE BORRACHA E DE MATERIAL PLÁSTICO</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L15" t="n">
         <v>2</v>
@@ -1942,68 +1830,68 @@
         <v>2</v>
       </c>
       <c r="N15" t="n">
+        <v>2</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2</v>
+      </c>
+      <c r="P15" t="n">
         <v>3</v>
       </c>
-      <c r="O15" t="n">
-        <v>5</v>
-      </c>
-      <c r="P15" t="n">
-        <v>7</v>
-      </c>
       <c r="Q15" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
-        <v>0.997849</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.838719</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.681521</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5693049999999999</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>0.455804</v>
+        <v>1.905261</v>
       </c>
       <c r="W15" t="n">
-        <v>0.307882</v>
+        <v>3.012845</v>
       </c>
       <c r="X15" t="n">
-        <v>0.20807</v>
+        <v>2.362606</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.341609</v>
+        <v>2.00286</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.281945</v>
+        <v>1.553699</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.340937</v>
+        <v>1.257806</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.422101</v>
+        <v>1.056689</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.483491</v>
+        <v>1.276719</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.795136</v>
+        <v>1.075124</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.517259</v>
+        <v>1.192585</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.279553</v>
+        <v>0.059904</v>
       </c>
       <c r="AG15" t="n">
-        <v>366.666667</v>
+        <v>50</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>5/12</t>
+          <t>3/12</t>
         </is>
       </c>
     </row>
@@ -2019,103 +1907,103 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>FABRICAÇÃO DE PRODUTOS DE METAL, EXCETO MÁQUINAS E EQUIPAMENTOS</t>
+          <t>FABRICAÇÃO DE PRODUTOS DE MINERAIS NÃO-METÁLICOS</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3</v>
+      </c>
+      <c r="O16" t="n">
+        <v>5</v>
+      </c>
+      <c r="P16" t="n">
         <v>7</v>
       </c>
-      <c r="K16" t="n">
-        <v>10</v>
-      </c>
-      <c r="L16" t="n">
-        <v>12</v>
-      </c>
-      <c r="M16" t="n">
-        <v>15</v>
-      </c>
-      <c r="N16" t="n">
-        <v>22</v>
-      </c>
-      <c r="O16" t="n">
-        <v>26</v>
-      </c>
-      <c r="P16" t="n">
-        <v>34</v>
-      </c>
       <c r="Q16" t="n">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>0.997849</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>0.838719</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>0.681521</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>0.5693049999999999</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.455804</v>
       </c>
       <c r="W16" t="n">
-        <v>2.050408</v>
+        <v>0.307882</v>
       </c>
       <c r="X16" t="n">
-        <v>1.59566</v>
+        <v>0.20807</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.325155</v>
+        <v>0.341609</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.237692</v>
+        <v>0.281945</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.272512</v>
+        <v>0.340937</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.014231</v>
+        <v>0.422101</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.9360309999999999</v>
+        <v>0.483491</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.906761</v>
+        <v>0.795136</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.795265</v>
+        <v>0.517259</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.898562</v>
+        <v>0.279553</v>
       </c>
       <c r="AG16" t="n">
-        <v>104.545455</v>
+        <v>366.666667</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>8/12</t>
+          <t>5/12</t>
         </is>
       </c>
     </row>
@@ -2131,11 +2019,11 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FABRICAÇÃO DE MÁQUINAS E EQUIPAMENTOS</t>
+          <t>FABRICAÇÃO DE PRODUTOS DE METAL, EXCETO MÁQUINAS E EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2154,28 +2042,28 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="N17" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="O17" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="P17" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2193,41 +2081,41 @@
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.050408</v>
       </c>
       <c r="X17" t="n">
-        <v>2.219417</v>
+        <v>1.59566</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.700102</v>
+        <v>1.325155</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.490283</v>
+        <v>1.237692</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.349283</v>
+        <v>1.272512</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.093897</v>
+        <v>1.014231</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.897913</v>
+        <v>0.9360309999999999</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.818176</v>
+        <v>0.906761</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.736082</v>
+        <v>0.795265</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.019968</v>
+        <v>0.898562</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>104.545455</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>8/12</t>
         </is>
       </c>
     </row>
@@ -2243,103 +2131,103 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>FABRICAÇÃO DE VEÍCULOS AUTOMOTORES, REBOQUES E CARROCERIAS</t>
+          <t>FABRICAÇÃO DE MÁQUINAS E EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P18" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>4.310707</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>4.069342</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3.38562</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2.569172</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.867903</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.382945</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.927389</v>
+        <v>2.219417</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.68056</v>
+        <v>1.700102</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.655413</v>
+        <v>1.490283</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.151031</v>
+        <v>1.349283</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.806202</v>
+        <v>1.093897</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.188662</v>
+        <v>0.897913</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.758091</v>
+        <v>0.818176</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.519464</v>
+        <v>0.736082</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.179712</v>
+        <v>0.019968</v>
       </c>
       <c r="AG18" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>1/12</t>
         </is>
       </c>
     </row>
@@ -2355,105 +2243,103 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FABRICAÇÃO DE OUTROS EQUIPAMENTOS DE TRANSPORTE, EXCETO VEÍCULOS AUTOMOTORES</t>
+          <t>FABRICAÇÃO DE VEÍCULOS AUTOMOTORES, REBOQUES E CARROCERIAS</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>4.310707</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>4.069342</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3.38562</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.569172</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.867903</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.382945</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.927389</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.68056</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.655413</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.151031</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.806202</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.188662</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.758091</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>2.519464</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.179712</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>125</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>0/12</t>
+          <t>4/12</t>
         </is>
       </c>
     </row>
@@ -2469,11 +2355,11 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>FABRICAÇÃO DE MÓVEIS</t>
+          <t>FABRICAÇÃO DE OUTROS EQUIPAMENTOS DE TRANSPORTE, EXCETO VEÍCULOS AUTOMOTORES</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2489,31 +2375,31 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2528,44 +2414,46 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>0.992323</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.240583</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.151585</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.821397</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.770023</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.8296829999999999</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.749799</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.81662</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.049583</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.647815</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.539137</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>200</v>
+        <v>0</v>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>8/12</t>
+          <t>0/12</t>
         </is>
       </c>
     </row>
@@ -2581,11 +2469,11 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>FABRICAÇÃO DE PRODUTOS DIVERSOS</t>
+          <t>FABRICAÇÃO DE MÓVEIS</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2595,37 +2483,37 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="n">
         <v>3</v>
       </c>
-      <c r="J21" t="n">
-        <v>4</v>
-      </c>
       <c r="K21" t="n">
+        <v>5</v>
+      </c>
+      <c r="L21" t="n">
+        <v>5</v>
+      </c>
+      <c r="M21" t="n">
         <v>6</v>
       </c>
-      <c r="L21" t="n">
-        <v>11</v>
-      </c>
-      <c r="M21" t="n">
-        <v>11</v>
-      </c>
       <c r="N21" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="O21" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="P21" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="Q21" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2634,50 +2522,50 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.691134</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>4.174904</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>4.025199</v>
+        <v>0.992323</v>
       </c>
       <c r="W21" t="n">
-        <v>1.917265</v>
+        <v>1.240583</v>
       </c>
       <c r="X21" t="n">
-        <v>1.586443</v>
+        <v>1.151585</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.088696</v>
+        <v>0.821397</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.581225</v>
+        <v>0.770023</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.455109</v>
+        <v>0.8296829999999999</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.670251</v>
+        <v>0.749799</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.565326</v>
+        <v>0.81662</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.418518</v>
+        <v>1.049583</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.859544</v>
+        <v>0.647815</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.71885</v>
+        <v>0.539137</v>
       </c>
       <c r="AG21" t="n">
-        <v>157.142857</v>
+        <v>200</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>10/12</t>
+          <t>8/12</t>
         </is>
       </c>
     </row>
@@ -2693,235 +2581,235 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO, REPARAÇÃO E INSTALAÇÃO DE MÁQUINAS E EQUIPAMENTOS</t>
+          <t>FABRICAÇÃO DE PRODUTOS DIVERSOS</t>
         </is>
       </c>
       <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" t="n">
         <v>3</v>
       </c>
-      <c r="F22" t="n">
-        <v>3</v>
-      </c>
-      <c r="G22" t="n">
-        <v>3</v>
-      </c>
-      <c r="H22" t="n">
-        <v>3</v>
-      </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>4</v>
       </c>
-      <c r="J22" t="n">
-        <v>5</v>
-      </c>
       <c r="K22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L22" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M22" t="n">
         <v>11</v>
       </c>
       <c r="N22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O22" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="P22" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="Q22" t="n">
         <v>36</v>
       </c>
       <c r="R22" t="n">
-        <v>3.23303</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.866233</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.440796</v>
+        <v>2.691134</v>
       </c>
       <c r="U22" t="n">
-        <v>1.768195</v>
+        <v>4.174904</v>
       </c>
       <c r="V22" t="n">
-        <v>1.686071</v>
+        <v>4.025199</v>
       </c>
       <c r="W22" t="n">
-        <v>1.201704</v>
+        <v>1.917265</v>
       </c>
       <c r="X22" t="n">
-        <v>0.991655</v>
+        <v>1.586443</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.8550219999999999</v>
+        <v>2.088696</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.875968</v>
+        <v>1.581225</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.7125089999999999</v>
+        <v>1.455109</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.840052</v>
+        <v>1.670251</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.767364</v>
+        <v>1.565326</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.772047</v>
+        <v>1.418518</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.462357</v>
+        <v>1.859544</v>
       </c>
       <c r="AF22" t="n">
         <v>0.71885</v>
       </c>
       <c r="AG22" t="n">
-        <v>176.923077</v>
+        <v>157.142857</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>9/12</t>
+          <t>10/12</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ELETRICIDADE E GÁS</t>
+          <t>INDÚSTRIAS DE TRANSFORMAÇÃO</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ELETRICIDADE, GÁS E OUTRAS UTILIDADES</t>
+          <t>MANUTENÇÃO, REPARAÇÃO E INSTALAÇÃO DE MÁQUINAS E EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="N23" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="O23" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="P23" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>3.23303</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.866233</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.440796</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.768195</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.686071</v>
       </c>
       <c r="W23" t="n">
-        <v>4.962332</v>
+        <v>1.201704</v>
       </c>
       <c r="X23" t="n">
-        <v>4.068932</v>
+        <v>0.991655</v>
       </c>
       <c r="Y23" t="n">
-        <v>3.322926</v>
+        <v>0.8550219999999999</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.80861</v>
+        <v>0.875968</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.182664</v>
+        <v>0.7125089999999999</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.33908</v>
+        <v>0.840052</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.008766</v>
+        <v>0.767364</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.932544</v>
+        <v>0.772047</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.586604</v>
+        <v>1.462357</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.019968</v>
+        <v>0.71885</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>176.923077</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>9/12</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ÁGUA, ESGOTO, ATIVIDADES DE GESTÃO DE RESÍDUOS E DESCONTAMINAÇÃO</t>
+          <t>ELETRICIDADE E GÁS</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ESGOTO E ATIVIDADES RELACIONADAS</t>
+          <t>ELETRICIDADE, GÁS E OUTRAS UTILIDADES</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -2940,22 +2828,22 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P24" t="n">
         <v>1</v>
@@ -2979,39 +2867,37 @@
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>4.962332</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>4.068932</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>3.322926</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.80861</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.182664</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.33908</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.9078889999999999</v>
+        <v>1.008766</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.818176</v>
+        <v>0.932544</v>
       </c>
       <c r="AE24" t="n">
-        <v>0.132774</v>
+        <v>1.586604</v>
       </c>
       <c r="AF24" t="n">
         <v>0.019968</v>
       </c>
-      <c r="AG24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="AG24" t="n">
+        <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -3031,11 +2917,11 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>COLETA, TRATAMENTO E DISPOSIÇÃO DE RESÍDUOS; RECUPERAÇÃO DE MATERIAIS</t>
+          <t>ESGOTO E ATIVIDADES RELACIONADAS</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3060,22 +2946,22 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3099,147 +2985,149 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.454064</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.374481</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.541683</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.693452</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.492229</v>
+        <v>0.9078889999999999</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.472882</v>
+        <v>0.818176</v>
       </c>
       <c r="AE25" t="n">
-        <v>0.232984</v>
+        <v>0.132774</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.09984</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>150</v>
+        <v>0.019968</v>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>1/12</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CONSTRUÇÃO</t>
+          <t>ÁGUA, ESGOTO, ATIVIDADES DE GESTÃO DE RESÍDUOS E DESCONTAMINAÇÃO</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>CONSTRUÇÃO DE EDIFÍCIOS</t>
+          <t>COLETA, TRATAMENTO E DISPOSIÇÃO DE RESÍDUOS; RECUPERAÇÃO DE MATERIAIS</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2</v>
+      </c>
+      <c r="O26" t="n">
         <v>4</v>
       </c>
-      <c r="H26" t="n">
+      <c r="P26" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q26" t="n">
         <v>5</v>
       </c>
-      <c r="I26" t="n">
-        <v>6</v>
-      </c>
-      <c r="J26" t="n">
-        <v>9</v>
-      </c>
-      <c r="K26" t="n">
-        <v>13</v>
-      </c>
-      <c r="L26" t="n">
-        <v>18</v>
-      </c>
-      <c r="M26" t="n">
-        <v>21</v>
-      </c>
-      <c r="N26" t="n">
-        <v>25</v>
-      </c>
-      <c r="O26" t="n">
-        <v>27</v>
-      </c>
-      <c r="P26" t="n">
-        <v>34</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>42</v>
-      </c>
       <c r="R26" t="n">
-        <v>0.573232</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0.511034</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>0.543804</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>0.545739</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>0.504928</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>0.536184</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>0.525748</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.606955</v>
+        <v>0.454064</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.605887</v>
+        <v>0.374481</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.625089</v>
+        <v>0.541683</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.556972</v>
+        <v>0.693452</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.608974</v>
+        <v>0.492229</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.670073</v>
+        <v>0.472882</v>
       </c>
       <c r="AE26" t="n">
-        <v>0.5703549999999999</v>
+        <v>0.232984</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.838658</v>
+        <v>0.09984</v>
       </c>
       <c r="AG26" t="n">
-        <v>68</v>
+        <v>150</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>11/12</t>
+          <t>4/12</t>
         </is>
       </c>
     </row>
@@ -3255,103 +3143,103 @@
         </is>
       </c>
       <c r="C27" t="n">
+        <v>41</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>CONSTRUÇÃO DE EDIFÍCIOS</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>3</v>
+      </c>
+      <c r="F27" t="n">
+        <v>3</v>
+      </c>
+      <c r="G27" t="n">
+        <v>4</v>
+      </c>
+      <c r="H27" t="n">
+        <v>5</v>
+      </c>
+      <c r="I27" t="n">
+        <v>6</v>
+      </c>
+      <c r="J27" t="n">
+        <v>9</v>
+      </c>
+      <c r="K27" t="n">
+        <v>13</v>
+      </c>
+      <c r="L27" t="n">
+        <v>18</v>
+      </c>
+      <c r="M27" t="n">
+        <v>21</v>
+      </c>
+      <c r="N27" t="n">
+        <v>25</v>
+      </c>
+      <c r="O27" t="n">
+        <v>27</v>
+      </c>
+      <c r="P27" t="n">
+        <v>34</v>
+      </c>
+      <c r="Q27" t="n">
         <v>42</v>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>OBRAS DE INFRA-ESTRUTURA</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>1</v>
-      </c>
-      <c r="J27" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" t="n">
-        <v>2</v>
-      </c>
-      <c r="L27" t="n">
-        <v>2</v>
-      </c>
-      <c r="M27" t="n">
-        <v>2</v>
-      </c>
-      <c r="N27" t="n">
-        <v>3</v>
-      </c>
-      <c r="O27" t="n">
-        <v>3</v>
-      </c>
-      <c r="P27" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>5</v>
-      </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>0.573232</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>0.511034</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>0.543804</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>0.545739</v>
       </c>
       <c r="V27" t="n">
-        <v>0.41782</v>
+        <v>0.504928</v>
       </c>
       <c r="W27" t="n">
-        <v>0.294964</v>
+        <v>0.536184</v>
       </c>
       <c r="X27" t="n">
-        <v>0.394829</v>
+        <v>0.525748</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.342409</v>
+        <v>0.606955</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.295643</v>
+        <v>0.605887</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.371672</v>
+        <v>0.625089</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.302991</v>
+        <v>0.556972</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.261054</v>
+        <v>0.608974</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.392784</v>
+        <v>0.670073</v>
       </c>
       <c r="AE27" t="n">
-        <v>0.236474</v>
+        <v>0.5703549999999999</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.09984</v>
+        <v>0.838658</v>
       </c>
       <c r="AG27" t="n">
-        <v>66.666667</v>
+        <v>68</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>11/12</t>
         </is>
       </c>
     </row>
@@ -3367,215 +3255,215 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>SERVIÇOS ESPECIALIZADOS PARA CONSTRUÇÃO</t>
+          <t>OBRAS DE INFRA-ESTRUTURA</t>
         </is>
       </c>
       <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
         <v>2</v>
       </c>
-      <c r="F28" t="n">
+      <c r="L28" t="n">
         <v>2</v>
       </c>
-      <c r="G28" t="n">
+      <c r="M28" t="n">
+        <v>2</v>
+      </c>
+      <c r="N28" t="n">
         <v>3</v>
       </c>
-      <c r="H28" t="n">
+      <c r="O28" t="n">
         <v>3</v>
       </c>
-      <c r="I28" t="n">
-        <v>4</v>
-      </c>
-      <c r="J28" t="n">
-        <v>14</v>
-      </c>
-      <c r="K28" t="n">
-        <v>23</v>
-      </c>
-      <c r="L28" t="n">
-        <v>31</v>
-      </c>
-      <c r="M28" t="n">
-        <v>43</v>
-      </c>
-      <c r="N28" t="n">
-        <v>68</v>
-      </c>
-      <c r="O28" t="n">
-        <v>104</v>
-      </c>
       <c r="P28" t="n">
-        <v>141</v>
+        <v>3</v>
       </c>
       <c r="Q28" t="n">
-        <v>184</v>
+        <v>5</v>
       </c>
       <c r="R28" t="n">
-        <v>0.879736</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0.744897</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>0.865007</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>0.689434</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>0.662699</v>
+        <v>0.41782</v>
       </c>
       <c r="W28" t="n">
-        <v>1.172825</v>
+        <v>0.294964</v>
       </c>
       <c r="X28" t="n">
-        <v>1.020314</v>
+        <v>0.394829</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.945052</v>
+        <v>0.342409</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.930102</v>
+        <v>0.295643</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.9492699999999999</v>
+        <v>0.371672</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.937481</v>
+        <v>0.302991</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.874667</v>
+        <v>0.261054</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.827596</v>
+        <v>0.392784</v>
       </c>
       <c r="AE28" t="n">
-        <v>0.884545</v>
+        <v>0.236474</v>
       </c>
       <c r="AF28" t="n">
-        <v>3.674121</v>
+        <v>0.09984</v>
       </c>
       <c r="AG28" t="n">
-        <v>170.588235</v>
+        <v>66.666667</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>10/12</t>
+          <t>4/12</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>COMÉRCIO; REPARAÇÃO DE VEÍCULOS AUTOMOTORES E MOTOCICLETAS</t>
+          <t>CONSTRUÇÃO</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>COMÉRCIO E REPARAÇÃO DE VEÍCULOS AUTOMOTORES E MOTOCICLETAS</t>
+          <t>SERVIÇOS ESPECIALIZADOS PARA CONSTRUÇÃO</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F29" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="G29" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="H29" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="I29" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="J29" t="n">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="K29" t="n">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="L29" t="n">
-        <v>102</v>
+        <v>31</v>
       </c>
       <c r="M29" t="n">
-        <v>120</v>
+        <v>43</v>
       </c>
       <c r="N29" t="n">
-        <v>161</v>
+        <v>68</v>
       </c>
       <c r="O29" t="n">
-        <v>218</v>
+        <v>104</v>
       </c>
       <c r="P29" t="n">
-        <v>290</v>
+        <v>141</v>
       </c>
       <c r="Q29" t="n">
-        <v>372</v>
+        <v>184</v>
       </c>
       <c r="R29" t="n">
-        <v>1.489252</v>
+        <v>0.879736</v>
       </c>
       <c r="S29" t="n">
-        <v>1.478612</v>
+        <v>0.744897</v>
       </c>
       <c r="T29" t="n">
-        <v>1.606442</v>
+        <v>0.865007</v>
       </c>
       <c r="U29" t="n">
-        <v>1.809125</v>
+        <v>0.689434</v>
       </c>
       <c r="V29" t="n">
-        <v>1.91952</v>
+        <v>0.662699</v>
       </c>
       <c r="W29" t="n">
-        <v>1.677254</v>
+        <v>1.172825</v>
       </c>
       <c r="X29" t="n">
-        <v>1.579474</v>
+        <v>1.020314</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.474811</v>
+        <v>0.945052</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.338864</v>
+        <v>0.930102</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.324308</v>
+        <v>0.9492699999999999</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.293159</v>
+        <v>0.937481</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.296346</v>
+        <v>0.874667</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.283919</v>
+        <v>0.827596</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.505468</v>
+        <v>0.884545</v>
       </c>
       <c r="AF29" t="n">
-        <v>7.428115</v>
+        <v>3.674121</v>
       </c>
       <c r="AG29" t="n">
-        <v>131.055901</v>
+        <v>170.588235</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>12/12</t>
+          <t>10/12</t>
         </is>
       </c>
     </row>
@@ -3591,99 +3479,99 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>COMÉRCIO POR ATACADO, EXCETO VEÍCULOS AUTOMOTORES E MOTOCICLETAS</t>
+          <t>COMÉRCIO E REPARAÇÃO DE VEÍCULOS AUTOMOTORES E MOTOCICLETAS</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I30" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="J30" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="K30" t="n">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="L30" t="n">
-        <v>58</v>
+        <v>102</v>
       </c>
       <c r="M30" t="n">
-        <v>64</v>
+        <v>120</v>
       </c>
       <c r="N30" t="n">
-        <v>80</v>
+        <v>161</v>
       </c>
       <c r="O30" t="n">
-        <v>109</v>
+        <v>218</v>
       </c>
       <c r="P30" t="n">
-        <v>160</v>
+        <v>290</v>
       </c>
       <c r="Q30" t="n">
-        <v>213</v>
+        <v>372</v>
       </c>
       <c r="R30" t="n">
-        <v>0.825455</v>
+        <v>1.489252</v>
       </c>
       <c r="S30" t="n">
-        <v>0.93442</v>
+        <v>1.478612</v>
       </c>
       <c r="T30" t="n">
-        <v>1.065843</v>
+        <v>1.606442</v>
       </c>
       <c r="U30" t="n">
-        <v>1.278032</v>
+        <v>1.809125</v>
       </c>
       <c r="V30" t="n">
-        <v>1.278699</v>
+        <v>1.91952</v>
       </c>
       <c r="W30" t="n">
-        <v>1.112692</v>
+        <v>1.677254</v>
       </c>
       <c r="X30" t="n">
-        <v>1.024785</v>
+        <v>1.579474</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.995318</v>
+        <v>1.474811</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.91548</v>
+        <v>1.338864</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.90722</v>
+        <v>1.324308</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.965078</v>
+        <v>1.293159</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.103724</v>
+        <v>1.296346</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.117733</v>
+        <v>1.283919</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.040345</v>
+        <v>1.505468</v>
       </c>
       <c r="AF30" t="n">
-        <v>4.253195</v>
+        <v>7.428115</v>
       </c>
       <c r="AG30" t="n">
-        <v>166.25</v>
+        <v>131.055901</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -3703,99 +3591,99 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>COMÉRCIO VAREJISTA</t>
+          <t>COMÉRCIO POR ATACADO, EXCETO VEÍCULOS AUTOMOTORES E MOTOCICLETAS</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>53</v>
+        <v>9</v>
       </c>
       <c r="F31" t="n">
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="G31" t="n">
-        <v>75</v>
+        <v>17</v>
       </c>
       <c r="H31" t="n">
-        <v>89</v>
+        <v>25</v>
       </c>
       <c r="I31" t="n">
+        <v>32</v>
+      </c>
+      <c r="J31" t="n">
+        <v>38</v>
+      </c>
+      <c r="K31" t="n">
+        <v>49</v>
+      </c>
+      <c r="L31" t="n">
+        <v>58</v>
+      </c>
+      <c r="M31" t="n">
+        <v>64</v>
+      </c>
+      <c r="N31" t="n">
+        <v>80</v>
+      </c>
+      <c r="O31" t="n">
         <v>109</v>
       </c>
-      <c r="J31" t="n">
-        <v>191</v>
-      </c>
-      <c r="K31" t="n">
-        <v>333</v>
-      </c>
-      <c r="L31" t="n">
-        <v>439</v>
-      </c>
-      <c r="M31" t="n">
-        <v>571</v>
-      </c>
-      <c r="N31" t="n">
-        <v>764</v>
-      </c>
-      <c r="O31" t="n">
-        <v>1069</v>
-      </c>
       <c r="P31" t="n">
-        <v>1390</v>
+        <v>160</v>
       </c>
       <c r="Q31" t="n">
-        <v>1730</v>
+        <v>213</v>
       </c>
       <c r="R31" t="n">
-        <v>1.209591</v>
+        <v>0.825455</v>
       </c>
       <c r="S31" t="n">
-        <v>1.20291</v>
+        <v>0.93442</v>
       </c>
       <c r="T31" t="n">
-        <v>1.143458</v>
+        <v>1.065843</v>
       </c>
       <c r="U31" t="n">
-        <v>1.09701</v>
+        <v>1.278032</v>
       </c>
       <c r="V31" t="n">
-        <v>1.0439</v>
+        <v>1.278699</v>
       </c>
       <c r="W31" t="n">
-        <v>1.051399</v>
+        <v>1.112692</v>
       </c>
       <c r="X31" t="n">
-        <v>1.137661</v>
+        <v>1.024785</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.151477</v>
+        <v>0.995318</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.158046</v>
+        <v>0.91548</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.159398</v>
+        <v>0.90722</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.176734</v>
+        <v>0.965078</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.1894</v>
+        <v>1.103724</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.191612</v>
+        <v>1.117733</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.147123</v>
+        <v>1.040345</v>
       </c>
       <c r="AF31" t="n">
-        <v>34.544728</v>
+        <v>4.253195</v>
       </c>
       <c r="AG31" t="n">
-        <v>126.439791</v>
+        <v>166.25</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -3806,112 +3694,112 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>TRANSPORTE, ARMAZENAGEM E CORREIO</t>
+          <t>COMÉRCIO; REPARAÇÃO DE VEÍCULOS AUTOMOTORES E MOTOCICLETAS</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>TRANSPORTE TERRESTRE</t>
+          <t>COMÉRCIO VAREJISTA</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="F32" t="n">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="G32" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="H32" t="n">
-        <v>7</v>
+        <v>89</v>
       </c>
       <c r="I32" t="n">
-        <v>7</v>
+        <v>109</v>
       </c>
       <c r="J32" t="n">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="K32" t="n">
-        <v>42</v>
+        <v>333</v>
       </c>
       <c r="L32" t="n">
-        <v>56</v>
+        <v>439</v>
       </c>
       <c r="M32" t="n">
-        <v>81</v>
+        <v>571</v>
       </c>
       <c r="N32" t="n">
-        <v>104</v>
+        <v>764</v>
       </c>
       <c r="O32" t="n">
-        <v>125</v>
+        <v>1069</v>
       </c>
       <c r="P32" t="n">
-        <v>165</v>
+        <v>1390</v>
       </c>
       <c r="Q32" t="n">
-        <v>232</v>
+        <v>1730</v>
       </c>
       <c r="R32" t="n">
-        <v>0.682074</v>
+        <v>1.209591</v>
       </c>
       <c r="S32" t="n">
-        <v>0.860618</v>
+        <v>1.20291</v>
       </c>
       <c r="T32" t="n">
-        <v>1.109453</v>
+        <v>1.143458</v>
       </c>
       <c r="U32" t="n">
-        <v>1.211371</v>
+        <v>1.09701</v>
       </c>
       <c r="V32" t="n">
-        <v>0.913481</v>
+        <v>1.0439</v>
       </c>
       <c r="W32" t="n">
-        <v>2.416959</v>
+        <v>1.051399</v>
       </c>
       <c r="X32" t="n">
-        <v>1.964312</v>
+        <v>1.137661</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.887434</v>
+        <v>1.151477</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.046689</v>
+        <v>1.158046</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.755265</v>
+        <v>1.159398</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.447277</v>
+        <v>1.176734</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.251825</v>
+        <v>1.1894</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.095415</v>
+        <v>1.191612</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.434013</v>
+        <v>1.147123</v>
       </c>
       <c r="AF32" t="n">
-        <v>4.632588</v>
+        <v>34.544728</v>
       </c>
       <c r="AG32" t="n">
-        <v>123.076923</v>
+        <v>126.439791</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>11/12</t>
+          <t>12/12</t>
         </is>
       </c>
     </row>
@@ -3927,103 +3815,103 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ARMAZENAMENTO E ATIVIDADES AUXILIARES DOS TRANSPORTES</t>
+          <t>TRANSPORTE TERRESTRE</t>
         </is>
       </c>
       <c r="E33" t="n">
         <v>2</v>
       </c>
       <c r="F33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H33" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I33" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J33" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="K33" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="L33" t="n">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="M33" t="n">
-        <v>3</v>
+        <v>81</v>
       </c>
       <c r="N33" t="n">
-        <v>5</v>
+        <v>104</v>
       </c>
       <c r="O33" t="n">
-        <v>5</v>
+        <v>125</v>
       </c>
       <c r="P33" t="n">
-        <v>6</v>
+        <v>165</v>
       </c>
       <c r="Q33" t="n">
-        <v>8</v>
+        <v>232</v>
       </c>
       <c r="R33" t="n">
-        <v>2.873805</v>
+        <v>0.682074</v>
       </c>
       <c r="S33" t="n">
-        <v>2.616006</v>
+        <v>0.860618</v>
       </c>
       <c r="T33" t="n">
-        <v>3.086889</v>
+        <v>1.109453</v>
       </c>
       <c r="U33" t="n">
-        <v>2.484241</v>
+        <v>1.211371</v>
       </c>
       <c r="V33" t="n">
-        <v>1.95746</v>
+        <v>0.913481</v>
       </c>
       <c r="W33" t="n">
-        <v>1.31129</v>
+        <v>2.416959</v>
       </c>
       <c r="X33" t="n">
-        <v>0.845086</v>
+        <v>1.964312</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.646941</v>
+        <v>1.887434</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.505939</v>
+        <v>2.046689</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.56391</v>
+        <v>1.755265</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.337681</v>
+        <v>1.447277</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.293569</v>
+        <v>1.251825</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.2988</v>
+        <v>1.095415</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.370894</v>
+        <v>1.434013</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.159744</v>
+        <v>4.632588</v>
       </c>
       <c r="AG33" t="n">
-        <v>60</v>
+        <v>123.076923</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>11/12</t>
         </is>
       </c>
     </row>
@@ -4039,215 +3927,215 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>CORREIO E OUTRAS ATIVIDADES DE ENTREGA</t>
+          <t>ARMAZENAMENTO E ATIVIDADES AUXILIARES DOS TRANSPORTES</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N34" t="n">
         <v>5</v>
       </c>
       <c r="O34" t="n">
+        <v>5</v>
+      </c>
+      <c r="P34" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q34" t="n">
         <v>8</v>
       </c>
-      <c r="P34" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>50</v>
-      </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.873805</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.616006</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>3.086889</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>2.484241</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.95746</v>
       </c>
       <c r="W34" t="n">
-        <v>2.19116</v>
+        <v>1.31129</v>
       </c>
       <c r="X34" t="n">
-        <v>2.503958</v>
+        <v>0.845086</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.783034</v>
+        <v>0.646941</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.383028</v>
+        <v>0.505939</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.668564</v>
+        <v>0.56391</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.5503400000000001</v>
+        <v>0.337681</v>
       </c>
       <c r="AC34" t="n">
-        <v>0.411292</v>
+        <v>0.293569</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.651003</v>
+        <v>0.2988</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.780183</v>
+        <v>1.370894</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.998403</v>
+        <v>0.159744</v>
       </c>
       <c r="AG34" t="n">
-        <v>900</v>
+        <v>60</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>6/12</t>
+          <t>4/12</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ALOJAMENTO E ALIMENTAÇÃO</t>
+          <t>TRANSPORTE, ARMAZENAGEM E CORREIO</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ALOJAMENTO</t>
+          <t>CORREIO E OUTRAS ATIVIDADES DE ENTREGA</t>
         </is>
       </c>
       <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
         <v>2</v>
       </c>
-      <c r="F35" t="n">
-        <v>2</v>
-      </c>
-      <c r="G35" t="n">
-        <v>2</v>
-      </c>
-      <c r="H35" t="n">
-        <v>3</v>
-      </c>
-      <c r="I35" t="n">
-        <v>3</v>
-      </c>
-      <c r="J35" t="n">
+      <c r="K35" t="n">
+        <v>4</v>
+      </c>
+      <c r="L35" t="n">
+        <v>4</v>
+      </c>
+      <c r="M35" t="n">
         <v>5</v>
       </c>
-      <c r="K35" t="n">
-        <v>7</v>
-      </c>
-      <c r="L35" t="n">
-        <v>7</v>
-      </c>
-      <c r="M35" t="n">
-        <v>11</v>
-      </c>
       <c r="N35" t="n">
+        <v>5</v>
+      </c>
+      <c r="O35" t="n">
+        <v>8</v>
+      </c>
+      <c r="P35" t="n">
         <v>12</v>
       </c>
-      <c r="O35" t="n">
-        <v>16</v>
-      </c>
-      <c r="P35" t="n">
-        <v>17</v>
-      </c>
       <c r="Q35" t="n">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="R35" t="n">
-        <v>0.901822</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0.763002</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>0.628468</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>0.784838</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>0.628108</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>0.725987</v>
+        <v>2.19116</v>
       </c>
       <c r="X35" t="n">
-        <v>0.720064</v>
+        <v>2.503958</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.619529</v>
+        <v>1.783034</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.839355</v>
+        <v>1.383028</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.773698</v>
+        <v>0.668564</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.862963</v>
+        <v>0.5503400000000001</v>
       </c>
       <c r="AC35" t="n">
-        <v>0.779939</v>
+        <v>0.411292</v>
       </c>
       <c r="AD35" t="n">
-        <v>0.717998</v>
+        <v>0.651003</v>
       </c>
       <c r="AE35" t="n">
-        <v>0.749675</v>
+        <v>0.780183</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.379393</v>
+        <v>0.998403</v>
       </c>
       <c r="AG35" t="n">
-        <v>58.333333</v>
+        <v>900</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>8/12</t>
+          <t>6/12</t>
         </is>
       </c>
     </row>
@@ -4263,123 +4151,123 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ALIMENTAÇÃO</t>
+          <t>ALOJAMENTO</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I36" t="n">
         <v>3</v>
       </c>
       <c r="J36" t="n">
+        <v>5</v>
+      </c>
+      <c r="K36" t="n">
+        <v>7</v>
+      </c>
+      <c r="L36" t="n">
+        <v>7</v>
+      </c>
+      <c r="M36" t="n">
+        <v>11</v>
+      </c>
+      <c r="N36" t="n">
+        <v>12</v>
+      </c>
+      <c r="O36" t="n">
+        <v>16</v>
+      </c>
+      <c r="P36" t="n">
         <v>17</v>
       </c>
-      <c r="K36" t="n">
-        <v>45</v>
-      </c>
-      <c r="L36" t="n">
-        <v>62</v>
-      </c>
-      <c r="M36" t="n">
-        <v>89</v>
-      </c>
-      <c r="N36" t="n">
-        <v>133</v>
-      </c>
-      <c r="O36" t="n">
-        <v>190</v>
-      </c>
-      <c r="P36" t="n">
-        <v>259</v>
-      </c>
       <c r="Q36" t="n">
-        <v>341</v>
+        <v>19</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>0.901822</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>0.763002</v>
       </c>
       <c r="T36" t="n">
-        <v>0.262386</v>
+        <v>0.628468</v>
       </c>
       <c r="U36" t="n">
-        <v>0.211834</v>
+        <v>0.784838</v>
       </c>
       <c r="V36" t="n">
-        <v>0.473161</v>
+        <v>0.628108</v>
       </c>
       <c r="W36" t="n">
-        <v>1.115174</v>
+        <v>0.725987</v>
       </c>
       <c r="X36" t="n">
-        <v>1.475307</v>
+        <v>0.720064</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.29982</v>
+        <v>0.619529</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.305831</v>
+        <v>0.839355</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.219573</v>
+        <v>0.773698</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.05616</v>
+        <v>0.862963</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.992399</v>
+        <v>0.779939</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.920527</v>
+        <v>0.717998</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.794782</v>
+        <v>0.749675</v>
       </c>
       <c r="AF36" t="n">
-        <v>6.809105</v>
+        <v>0.379393</v>
       </c>
       <c r="AG36" t="n">
-        <v>156.390977</v>
+        <v>58.333333</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>10/12</t>
+          <t>8/12</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>I</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>INFORMAÇÃO E COMUNICAÇÃO</t>
+          <t>ALOJAMENTO E ALIMENTAÇÃO</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>EDIÇÃO E EDIÇÃO INTEGRADA À IMPRESSÃO</t>
+          <t>ALIMENTAÇÃO</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -4389,37 +4277,37 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K37" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="L37" t="n">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="M37" t="n">
-        <v>2</v>
+        <v>89</v>
       </c>
       <c r="N37" t="n">
-        <v>3</v>
+        <v>133</v>
       </c>
       <c r="O37" t="n">
-        <v>3</v>
+        <v>190</v>
       </c>
       <c r="P37" t="n">
-        <v>4</v>
+        <v>259</v>
       </c>
       <c r="Q37" t="n">
-        <v>7</v>
+        <v>341</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -4428,50 +4316,50 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>0.262386</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>0.211834</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>0.473161</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.115174</v>
       </c>
       <c r="X37" t="n">
-        <v>1.64586</v>
+        <v>1.475307</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.133401</v>
+        <v>1.29982</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.768672</v>
+        <v>1.305831</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.689262</v>
+        <v>1.219573</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.396259</v>
+        <v>1.05616</v>
       </c>
       <c r="AC37" t="n">
-        <v>0.312467</v>
+        <v>0.992399</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.362873</v>
+        <v>0.920527</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.408369</v>
+        <v>0.794782</v>
       </c>
       <c r="AF37" t="n">
-        <v>0.139776</v>
+        <v>6.809105</v>
       </c>
       <c r="AG37" t="n">
-        <v>133.333333</v>
+        <v>156.390977</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>10/12</t>
         </is>
       </c>
     </row>
@@ -4487,11 +4375,11 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ATIVIDADES CINEMATOGRÁFICAS, PRODUÇÃO DE VÍDEOS E DE PROGRAMAS DE TELEVISÃO; GRAVAÇÃO DE SOM E EDIÇÃO DE MÚSICA</t>
+          <t>EDIÇÃO E EDIÇÃO INTEGRADA À IMPRESSÃO</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4513,25 +4401,25 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P38" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q38" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -4552,38 +4440,38 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.64586</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.133401</v>
       </c>
       <c r="Z38" t="n">
-        <v>0.42704</v>
+        <v>0.768672</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.249029</v>
+        <v>0.689262</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.144094</v>
+        <v>0.396259</v>
       </c>
       <c r="AC38" t="n">
-        <v>0.530011</v>
+        <v>0.312467</v>
       </c>
       <c r="AD38" t="n">
-        <v>0.721434</v>
+        <v>0.362873</v>
       </c>
       <c r="AE38" t="n">
-        <v>0.159354</v>
+        <v>0.408369</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.279553</v>
+        <v>0.139776</v>
       </c>
       <c r="AG38" t="n">
-        <v>1300</v>
+        <v>133.333333</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>4/12</t>
         </is>
       </c>
     </row>
@@ -4599,103 +4487,103 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ATIVIDADES DE RÁDIO E DE TELEVISÃO</t>
+          <t>ATIVIDADES CINEMATOGRÁFICAS, PRODUÇÃO DE VÍDEOS E DE PROGRAMAS DE TELEVISÃO; GRAVAÇÃO DE SOM E EDIÇÃO DE MÚSICA</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P39" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q39" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="R39" t="n">
-        <v>1.87422</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>1.831204</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>1.66594</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>1.529736</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.411304</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.67602</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.307871</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.253218</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.177804</v>
+        <v>0.42704</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.13011</v>
+        <v>0.249029</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.068807</v>
+        <v>0.144094</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.021375</v>
+        <v>0.530011</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.294427</v>
+        <v>0.721434</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.403234</v>
+        <v>0.159354</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.079872</v>
+        <v>0.279553</v>
       </c>
       <c r="AG39" t="n">
-        <v>33.333333</v>
+        <v>1300</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>3/12</t>
         </is>
       </c>
     </row>
@@ -4711,103 +4599,103 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>TELECOMUNICAÇÕES</t>
+          <t>ATIVIDADES DE RÁDIO E DE TELEVISÃO</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K40" t="n">
+        <v>3</v>
+      </c>
+      <c r="L40" t="n">
+        <v>3</v>
+      </c>
+      <c r="M40" t="n">
+        <v>3</v>
+      </c>
+      <c r="N40" t="n">
+        <v>3</v>
+      </c>
+      <c r="O40" t="n">
+        <v>3</v>
+      </c>
+      <c r="P40" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q40" t="n">
         <v>4</v>
       </c>
-      <c r="L40" t="n">
-        <v>4</v>
-      </c>
-      <c r="M40" t="n">
-        <v>4</v>
-      </c>
-      <c r="N40" t="n">
-        <v>6</v>
-      </c>
-      <c r="O40" t="n">
-        <v>10</v>
-      </c>
-      <c r="P40" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>15</v>
-      </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.87422</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>1.831204</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>1.66594</v>
       </c>
       <c r="U40" t="n">
-        <v>1.077395</v>
+        <v>1.529736</v>
       </c>
       <c r="V40" t="n">
-        <v>0.732793</v>
+        <v>1.411304</v>
       </c>
       <c r="W40" t="n">
-        <v>0.843596</v>
+        <v>1.67602</v>
       </c>
       <c r="X40" t="n">
-        <v>1.073125</v>
+        <v>1.307871</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.786069</v>
+        <v>1.253218</v>
       </c>
       <c r="Z40" t="n">
-        <v>0.586537</v>
+        <v>1.177804</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.649072</v>
+        <v>1.13011</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.779004</v>
+        <v>1.068807</v>
       </c>
       <c r="AC40" t="n">
-        <v>0.763645</v>
+        <v>1.021375</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.788902</v>
+        <v>1.294427</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.621549</v>
+        <v>1.403234</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.299521</v>
+        <v>0.079872</v>
       </c>
       <c r="AG40" t="n">
-        <v>150</v>
+        <v>33.333333</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>7/12</t>
+          <t>2/12</t>
         </is>
       </c>
     </row>
@@ -4823,11 +4711,11 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ATIVIDADES DOS SERVIÇOS DE TECNOLOGIA DA INFORMAÇÃO</t>
+          <t>TELECOMUNICAÇÕES</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -4840,7 +4728,7 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" t="n">
         <v>1</v>
@@ -4849,25 +4737,25 @@
         <v>2</v>
       </c>
       <c r="K41" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L41" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N41" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O41" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="P41" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Q41" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -4879,47 +4767,47 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.077395</v>
       </c>
       <c r="V41" t="n">
-        <v>0.570437</v>
+        <v>0.732793</v>
       </c>
       <c r="W41" t="n">
-        <v>0.770408</v>
+        <v>0.843596</v>
       </c>
       <c r="X41" t="n">
-        <v>0.538535</v>
+        <v>1.073125</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.447122</v>
+        <v>0.786069</v>
       </c>
       <c r="Z41" t="n">
-        <v>0.564617</v>
+        <v>0.586537</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.431457</v>
+        <v>0.649072</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.421529</v>
+        <v>0.779004</v>
       </c>
       <c r="AC41" t="n">
-        <v>0.613702</v>
+        <v>0.763645</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.634585</v>
+        <v>0.788902</v>
       </c>
       <c r="AE41" t="n">
-        <v>0.38403</v>
+        <v>0.621549</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.179712</v>
+        <v>0.299521</v>
       </c>
       <c r="AG41" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>6/12</t>
+          <t>7/12</t>
         </is>
       </c>
     </row>
@@ -4935,11 +4823,11 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ATIVIDADES DE PRESTAÇÃO DE SERVIÇOS DE INFORMAÇÃO</t>
+          <t>ATIVIDADES DOS SERVIÇOS DE TECNOLOGIA DA INFORMAÇÃO</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -4955,31 +4843,31 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P42" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Q42" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -4994,66 +4882,64 @@
         <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>0.570437</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>0.770408</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>0.538535</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>0.447122</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>0.564617</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>0.431457</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>0.421529</v>
       </c>
       <c r="AC42" t="n">
-        <v>0.240324</v>
+        <v>0.613702</v>
       </c>
       <c r="AD42" t="n">
-        <v>0.179931</v>
+        <v>0.634585</v>
       </c>
       <c r="AE42" t="n">
-        <v>0.032327</v>
+        <v>0.38403</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.019968</v>
-      </c>
-      <c r="AG42" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.179712</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>200</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>6/12</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>J</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ATIVIDADES FINANCEIRAS, DE SEGUROS E SERVIÇOS RELACIONADOS</t>
+          <t>INFORMAÇÃO E COMUNICAÇÃO</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ATIVIDADES DE SERVIÇOS FINANCEIROS</t>
+          <t>ATIVIDADES DE PRESTAÇÃO DE SERVIÇOS DE INFORMAÇÃO</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -5081,19 +4967,19 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -5120,32 +5006,34 @@
         <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>0.45216</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.389557</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.738276</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>0.527162</v>
+        <v>0.240324</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.732714</v>
+        <v>0.179931</v>
       </c>
       <c r="AE43" t="n">
-        <v>0.218451</v>
+        <v>0.032327</v>
       </c>
       <c r="AF43" t="n">
-        <v>0.219649</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>450</v>
+        <v>0.019968</v>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>1/12</t>
         </is>
       </c>
     </row>
@@ -5161,11 +5049,11 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>SEGUROS, RESSEGUROS, PREVIDÊNCIA COMPLEMENTAR E PLANOS DE SAÚDE</t>
+          <t>ATIVIDADES DE SERVIÇOS FINANCEIROS</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -5193,19 +5081,19 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -5232,34 +5120,32 @@
         <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>0.45216</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>0.389557</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>0.738276</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>0.527162</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>0.732714</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>0.218451</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG44" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.219649</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>450</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>0/12</t>
+          <t>3/12</t>
         </is>
       </c>
     </row>
@@ -5275,327 +5161,329 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ATIVIDADES AUXILIARES DOS SERVIÇOS FINANCEIROS, SEGUROS, PREVIDÊNCIA COMPLEMENTAR E PLANOS DE SAÚDE</t>
+          <t>SEGUROS, RESSEGUROS, PREVIDÊNCIA COMPLEMENTAR E PLANOS DE SAÚDE</t>
         </is>
       </c>
       <c r="E45" t="n">
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>0.737398</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>0.586336</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>0.486397</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>0.429113</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>0.334761</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>0.248274</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.214382</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>0.35796</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.602114</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>0.507625</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>0.5312750000000001</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>0.462789</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>0.422956</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>0.09984</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>25</v>
+        <v>0</v>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>0/12</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>K</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ATIVIDADES IMOBILIÁRIAS</t>
+          <t>ATIVIDADES FINANCEIRAS, DE SEGUROS E SERVIÇOS RELACIONADOS</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ATIVIDADES IMOBILIÁRIAS</t>
+          <t>ATIVIDADES AUXILIARES DOS SERVIÇOS FINANCEIROS, SEGUROS, PREVIDÊNCIA COMPLEMENTAR E PLANOS DE SAÚDE</t>
         </is>
       </c>
       <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1</v>
+      </c>
+      <c r="M46" t="n">
         <v>2</v>
       </c>
-      <c r="F46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G46" t="n">
-        <v>2</v>
-      </c>
-      <c r="H46" t="n">
-        <v>2</v>
-      </c>
-      <c r="I46" t="n">
-        <v>3</v>
-      </c>
-      <c r="J46" t="n">
+      <c r="N46" t="n">
+        <v>4</v>
+      </c>
+      <c r="O46" t="n">
+        <v>4</v>
+      </c>
+      <c r="P46" t="n">
         <v>5</v>
       </c>
-      <c r="K46" t="n">
-        <v>9</v>
-      </c>
-      <c r="L46" t="n">
-        <v>9</v>
-      </c>
-      <c r="M46" t="n">
-        <v>10</v>
-      </c>
-      <c r="N46" t="n">
-        <v>13</v>
-      </c>
-      <c r="O46" t="n">
-        <v>15</v>
-      </c>
-      <c r="P46" t="n">
-        <v>16</v>
-      </c>
       <c r="Q46" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="R46" t="n">
-        <v>1.00249</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>0.89327</v>
+        <v>0.737398</v>
       </c>
       <c r="T46" t="n">
-        <v>0.736521</v>
+        <v>0.586336</v>
       </c>
       <c r="U46" t="n">
-        <v>0.6036010000000001</v>
+        <v>0.486397</v>
       </c>
       <c r="V46" t="n">
-        <v>0.669295</v>
+        <v>0.429113</v>
       </c>
       <c r="W46" t="n">
-        <v>0.751869</v>
+        <v>0.334761</v>
       </c>
       <c r="X46" t="n">
-        <v>0.883602</v>
+        <v>0.248274</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.721425</v>
+        <v>0.214382</v>
       </c>
       <c r="Z46" t="n">
-        <v>0.663853</v>
+        <v>0.35796</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.727555</v>
+        <v>0.602114</v>
       </c>
       <c r="AB46" t="n">
-        <v>0.684891</v>
+        <v>0.507625</v>
       </c>
       <c r="AC46" t="n">
-        <v>0.615808</v>
+        <v>0.5312750000000001</v>
       </c>
       <c r="AD46" t="n">
-        <v>0.593163</v>
+        <v>0.462789</v>
       </c>
       <c r="AE46" t="n">
-        <v>0.734411</v>
+        <v>0.422956</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.379393</v>
+        <v>0.09984</v>
       </c>
       <c r="AG46" t="n">
-        <v>46.153846</v>
+        <v>25</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>8/12</t>
+          <t>4/12</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ATIVIDADES PROFISSIONAIS, CIENTÍFICAS E TÉCNICAS</t>
+          <t>ATIVIDADES IMOBILIÁRIAS</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ATIVIDADES JURÍDICAS, DE CONTABILIDADE E DE AUDITORIA</t>
+          <t>ATIVIDADES IMOBILIÁRIAS</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F47" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G47" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H47" t="n">
+        <v>2</v>
+      </c>
+      <c r="I47" t="n">
+        <v>3</v>
+      </c>
+      <c r="J47" t="n">
+        <v>5</v>
+      </c>
+      <c r="K47" t="n">
+        <v>9</v>
+      </c>
+      <c r="L47" t="n">
+        <v>9</v>
+      </c>
+      <c r="M47" t="n">
         <v>10</v>
       </c>
-      <c r="I47" t="n">
-        <v>11</v>
-      </c>
-      <c r="J47" t="n">
+      <c r="N47" t="n">
         <v>13</v>
       </c>
-      <c r="K47" t="n">
-        <v>14</v>
-      </c>
-      <c r="L47" t="n">
-        <v>20</v>
-      </c>
-      <c r="M47" t="n">
-        <v>23</v>
-      </c>
-      <c r="N47" t="n">
-        <v>28</v>
-      </c>
       <c r="O47" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="P47" t="n">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="Q47" t="n">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="R47" t="n">
-        <v>1.483041</v>
+        <v>1.00249</v>
       </c>
       <c r="S47" t="n">
-        <v>1.592351</v>
+        <v>0.89327</v>
       </c>
       <c r="T47" t="n">
-        <v>1.333357</v>
+        <v>0.736521</v>
       </c>
       <c r="U47" t="n">
-        <v>1.51585</v>
+        <v>0.6036010000000001</v>
       </c>
       <c r="V47" t="n">
-        <v>1.282611</v>
+        <v>0.669295</v>
       </c>
       <c r="W47" t="n">
-        <v>1.023018</v>
+        <v>0.751869</v>
       </c>
       <c r="X47" t="n">
-        <v>0.775035</v>
+        <v>0.883602</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.926545</v>
+        <v>0.721425</v>
       </c>
       <c r="Z47" t="n">
-        <v>0.818493</v>
+        <v>0.663853</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.804451</v>
+        <v>0.727555</v>
       </c>
       <c r="AB47" t="n">
-        <v>0.967092</v>
+        <v>0.684891</v>
       </c>
       <c r="AC47" t="n">
-        <v>0.985884</v>
+        <v>0.615808</v>
       </c>
       <c r="AD47" t="n">
-        <v>0.9770180000000001</v>
+        <v>0.593163</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.114211</v>
+        <v>0.734411</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.198083</v>
+        <v>0.379393</v>
       </c>
       <c r="AG47" t="n">
-        <v>114.285714</v>
+        <v>46.153846</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>11/12</t>
+          <t>8/12</t>
         </is>
       </c>
     </row>
@@ -5611,103 +5499,103 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ATIVIDADES DE SEDES DE EMPRESAS E DE CONSULTORIA EM GESTÃO EMPRESARIAL</t>
+          <t>ATIVIDADES JURÍDICAS, DE CONTABILIDADE E DE AUDITORIA</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H48" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I48" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J48" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="K48" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="L48" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="M48" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="N48" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="O48" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="P48" t="n">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="Q48" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.483041</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>1.592351</v>
       </c>
       <c r="T48" t="n">
-        <v>1.140807</v>
+        <v>1.333357</v>
       </c>
       <c r="U48" t="n">
-        <v>0.801582</v>
+        <v>1.51585</v>
       </c>
       <c r="V48" t="n">
-        <v>1.221321</v>
+        <v>1.282611</v>
       </c>
       <c r="W48" t="n">
-        <v>0.7996180000000001</v>
+        <v>1.023018</v>
       </c>
       <c r="X48" t="n">
-        <v>1.081045</v>
+        <v>0.775035</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.029639</v>
+        <v>0.926545</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.172401</v>
+        <v>0.818493</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.16358</v>
+        <v>0.804451</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.035556</v>
+        <v>0.967092</v>
       </c>
       <c r="AC48" t="n">
-        <v>0.9999479999999999</v>
+        <v>0.985884</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.084083</v>
+        <v>0.9770180000000001</v>
       </c>
       <c r="AE48" t="n">
-        <v>0.886891</v>
+        <v>1.114211</v>
       </c>
       <c r="AF48" t="n">
-        <v>0.399361</v>
+        <v>1.198083</v>
       </c>
       <c r="AG48" t="n">
-        <v>122.222222</v>
+        <v>114.285714</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>9/12</t>
+          <t>11/12</t>
         </is>
       </c>
     </row>
@@ -5723,24 +5611,24 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE ARQUITETURA E ENGENHARIA; TESTES E ANÁLISES TÉCNICAS</t>
+          <t>ATIVIDADES DE SEDES DE EMPRESAS E DE CONSULTORIA EM GESTÃO EMPRESARIAL</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I49" t="n">
         <v>2</v>
@@ -5749,77 +5637,77 @@
         <v>2</v>
       </c>
       <c r="K49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L49" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M49" t="n">
         <v>7</v>
       </c>
       <c r="N49" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="O49" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="P49" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="Q49" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="R49" t="n">
-        <v>0.555503</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>0.935083</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>0.744356</v>
+        <v>1.140807</v>
       </c>
       <c r="U49" t="n">
-        <v>0.577508</v>
+        <v>0.801582</v>
       </c>
       <c r="V49" t="n">
-        <v>0.453634</v>
+        <v>1.221321</v>
       </c>
       <c r="W49" t="n">
-        <v>0.317142</v>
+        <v>0.7996180000000001</v>
       </c>
       <c r="X49" t="n">
-        <v>0.328434</v>
+        <v>1.081045</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.519084</v>
+        <v>1.029639</v>
       </c>
       <c r="Z49" t="n">
-        <v>0.466819</v>
+        <v>1.172401</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.588195</v>
+        <v>1.16358</v>
       </c>
       <c r="AB49" t="n">
-        <v>0.5952809999999999</v>
+        <v>1.035556</v>
       </c>
       <c r="AC49" t="n">
-        <v>0.593862</v>
+        <v>0.9999479999999999</v>
       </c>
       <c r="AD49" t="n">
-        <v>0.674661</v>
+        <v>1.084083</v>
       </c>
       <c r="AE49" t="n">
-        <v>0.565351</v>
+        <v>0.886891</v>
       </c>
       <c r="AF49" t="n">
-        <v>0.6190099999999999</v>
+        <v>0.399361</v>
       </c>
       <c r="AG49" t="n">
-        <v>158.333333</v>
+        <v>122.222222</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>8/12</t>
+          <t>9/12</t>
         </is>
       </c>
     </row>
@@ -5835,103 +5723,103 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>PUBLICIDADE E PESQUISA DE MERCADO</t>
+          <t>SERVIÇOS DE ARQUITETURA E ENGENHARIA; TESTES E ANÁLISES TÉCNICAS</t>
         </is>
       </c>
       <c r="E50" t="n">
         <v>1</v>
       </c>
       <c r="F50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H50" t="n">
         <v>2</v>
       </c>
       <c r="I50" t="n">
+        <v>2</v>
+      </c>
+      <c r="J50" t="n">
+        <v>2</v>
+      </c>
+      <c r="K50" t="n">
         <v>3</v>
       </c>
-      <c r="J50" t="n">
-        <v>8</v>
-      </c>
-      <c r="K50" t="n">
+      <c r="L50" t="n">
+        <v>6</v>
+      </c>
+      <c r="M50" t="n">
+        <v>7</v>
+      </c>
+      <c r="N50" t="n">
         <v>12</v>
       </c>
-      <c r="L50" t="n">
-        <v>15</v>
-      </c>
-      <c r="M50" t="n">
-        <v>23</v>
-      </c>
-      <c r="N50" t="n">
-        <v>39</v>
-      </c>
       <c r="O50" t="n">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="P50" t="n">
-        <v>104</v>
+        <v>22</v>
       </c>
       <c r="Q50" t="n">
-        <v>163</v>
+        <v>31</v>
       </c>
       <c r="R50" t="n">
-        <v>1.197419</v>
+        <v>0.555503</v>
       </c>
       <c r="S50" t="n">
-        <v>1.008002</v>
+        <v>0.935083</v>
       </c>
       <c r="T50" t="n">
-        <v>0.801177</v>
+        <v>0.744356</v>
       </c>
       <c r="U50" t="n">
-        <v>1.268325</v>
+        <v>0.577508</v>
       </c>
       <c r="V50" t="n">
-        <v>1.465585</v>
+        <v>0.453634</v>
       </c>
       <c r="W50" t="n">
-        <v>2.198297</v>
+        <v>0.317142</v>
       </c>
       <c r="X50" t="n">
-        <v>1.569445</v>
+        <v>0.328434</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.348789</v>
+        <v>0.519084</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.248735</v>
+        <v>0.466819</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.154453</v>
+        <v>0.588195</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.136333</v>
+        <v>0.5952809999999999</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.125095</v>
+        <v>0.593862</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.120339</v>
+        <v>0.674661</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.280154</v>
+        <v>0.565351</v>
       </c>
       <c r="AF50" t="n">
-        <v>3.254792</v>
+        <v>0.6190099999999999</v>
       </c>
       <c r="AG50" t="n">
-        <v>317.948718</v>
+        <v>158.333333</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>10/12</t>
+          <t>8/12</t>
         </is>
       </c>
     </row>
@@ -5947,103 +5835,103 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>OUTRAS ATIVIDADES PROFISSIONAIS, CIENTÍFICAS E TÉCNICAS</t>
+          <t>PUBLICIDADE E PESQUISA DE MERCADO</t>
         </is>
       </c>
       <c r="E51" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" t="n">
+        <v>1</v>
+      </c>
+      <c r="H51" t="n">
         <v>2</v>
-      </c>
-      <c r="F51" t="n">
-        <v>3</v>
-      </c>
-      <c r="G51" t="n">
-        <v>3</v>
-      </c>
-      <c r="H51" t="n">
-        <v>3</v>
       </c>
       <c r="I51" t="n">
         <v>3</v>
       </c>
       <c r="J51" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K51" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L51" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="M51" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="N51" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="O51" t="n">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="P51" t="n">
-        <v>19</v>
+        <v>104</v>
       </c>
       <c r="Q51" t="n">
-        <v>31</v>
+        <v>163</v>
       </c>
       <c r="R51" t="n">
-        <v>2.052718</v>
+        <v>1.197419</v>
       </c>
       <c r="S51" t="n">
-        <v>2.6582</v>
+        <v>1.008002</v>
       </c>
       <c r="T51" t="n">
-        <v>1.992802</v>
+        <v>0.801177</v>
       </c>
       <c r="U51" t="n">
-        <v>1.573786</v>
+        <v>1.268325</v>
       </c>
       <c r="V51" t="n">
-        <v>1.180947</v>
+        <v>1.465585</v>
       </c>
       <c r="W51" t="n">
-        <v>0.942566</v>
+        <v>2.198297</v>
       </c>
       <c r="X51" t="n">
-        <v>0.917421</v>
+        <v>1.569445</v>
       </c>
       <c r="Y51" t="n">
-        <v>0.789708</v>
+        <v>1.348789</v>
       </c>
       <c r="Z51" t="n">
-        <v>0.7814680000000001</v>
+        <v>1.248735</v>
       </c>
       <c r="AA51" t="n">
-        <v>0.625722</v>
+        <v>1.154453</v>
       </c>
       <c r="AB51" t="n">
-        <v>0.565957</v>
+        <v>1.136333</v>
       </c>
       <c r="AC51" t="n">
-        <v>0.595052</v>
+        <v>1.125095</v>
       </c>
       <c r="AD51" t="n">
-        <v>0.6997719999999999</v>
+        <v>1.120339</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.182778</v>
+        <v>1.280154</v>
       </c>
       <c r="AF51" t="n">
-        <v>0.6190099999999999</v>
+        <v>3.254792</v>
       </c>
       <c r="AG51" t="n">
-        <v>210</v>
+        <v>317.948718</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>9/12</t>
+          <t>10/12</t>
         </is>
       </c>
     </row>
@@ -6059,215 +5947,215 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ATIVIDADES VETERINÁRIAS</t>
+          <t>OUTRAS ATIVIDADES PROFISSIONAIS, CIENTÍFICAS E TÉCNICAS</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J52" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K52" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L52" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M52" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="N52" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O52" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="P52" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="Q52" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>2.052718</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>2.6582</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>1.992802</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>1.573786</v>
       </c>
       <c r="V52" t="n">
-        <v>3.663963</v>
+        <v>1.180947</v>
       </c>
       <c r="W52" t="n">
-        <v>2.811988</v>
+        <v>0.942566</v>
       </c>
       <c r="X52" t="n">
-        <v>1.877969</v>
+        <v>0.917421</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.075064</v>
+        <v>0.789708</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.587475</v>
+        <v>0.7814680000000001</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.215241</v>
+        <v>0.625722</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.438272</v>
+        <v>0.565957</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.343915</v>
+        <v>0.595052</v>
       </c>
       <c r="AD52" t="n">
-        <v>0.987775</v>
+        <v>0.6997719999999999</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.30782</v>
+        <v>1.182778</v>
       </c>
       <c r="AF52" t="n">
-        <v>0.09984</v>
+        <v>0.6190099999999999</v>
       </c>
       <c r="AG52" t="n">
-        <v>25</v>
+        <v>210</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>9/12</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ATIVIDADES ADMINISTRATIVAS E SERVIÇOS COMPLEMENTARES</t>
+          <t>ATIVIDADES PROFISSIONAIS, CIENTÍFICAS E TÉCNICAS</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ALUGUÉIS NÃO-IMOBILIÁRIOS E GESTÃO DE ATIVOS INTANGÍVEIS NÃO-FINANCEIROS</t>
+          <t>ATIVIDADES VETERINÁRIAS</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1</v>
+      </c>
+      <c r="J53" t="n">
+        <v>1</v>
+      </c>
+      <c r="K53" t="n">
+        <v>1</v>
+      </c>
+      <c r="L53" t="n">
+        <v>1</v>
+      </c>
+      <c r="M53" t="n">
         <v>2</v>
       </c>
-      <c r="H53" t="n">
-        <v>3</v>
-      </c>
-      <c r="I53" t="n">
+      <c r="N53" t="n">
         <v>4</v>
       </c>
-      <c r="J53" t="n">
-        <v>6</v>
-      </c>
-      <c r="K53" t="n">
-        <v>10</v>
-      </c>
-      <c r="L53" t="n">
-        <v>12</v>
-      </c>
-      <c r="M53" t="n">
-        <v>14</v>
-      </c>
-      <c r="N53" t="n">
-        <v>18</v>
-      </c>
       <c r="O53" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="P53" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="Q53" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="R53" t="n">
-        <v>0.476848</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>0.41936</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>0.670634</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>0.791035</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>0.807314</v>
+        <v>3.663963</v>
       </c>
       <c r="W53" t="n">
-        <v>0.8034249999999999</v>
+        <v>2.811988</v>
       </c>
       <c r="X53" t="n">
-        <v>0.876086</v>
+        <v>1.877969</v>
       </c>
       <c r="Y53" t="n">
-        <v>0.860051</v>
+        <v>1.075064</v>
       </c>
       <c r="Z53" t="n">
-        <v>0.806257</v>
+        <v>1.587475</v>
       </c>
       <c r="AA53" t="n">
-        <v>0.804209</v>
+        <v>2.215241</v>
       </c>
       <c r="AB53" t="n">
-        <v>0.89751</v>
+        <v>1.438272</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.018647</v>
+        <v>1.343915</v>
       </c>
       <c r="AD53" t="n">
-        <v>0.954929</v>
+        <v>0.987775</v>
       </c>
       <c r="AE53" t="n">
-        <v>0.783562</v>
+        <v>1.30782</v>
       </c>
       <c r="AF53" t="n">
-        <v>0.998403</v>
+        <v>0.09984</v>
       </c>
       <c r="AG53" t="n">
-        <v>177.777778</v>
+        <v>25</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>11/12</t>
+          <t>4/12</t>
         </is>
       </c>
     </row>
@@ -6283,105 +6171,103 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>SELEÇÃO, AGENCIAMENTO E LOCAÇÃO DE MÃO-DE-OBRA</t>
+          <t>ALUGUÉIS NÃO-IMOBILIÁRIOS E GESTÃO DE ATIVOS INTANGÍVEIS NÃO-FINANCEIROS</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>0.476848</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>0.41936</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>0.670634</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>0.791035</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>0.807314</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>0.8034249999999999</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>0.876086</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>0.860051</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>0.806257</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>0.804209</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>0.89751</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>1.018647</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>0.954929</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>0.783562</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG54" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.998403</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>177.777778</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>0/12</t>
+          <t>11/12</t>
         </is>
       </c>
     </row>
@@ -6397,103 +6283,105 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>AGÊNCIAS DE VIAGENS, OPERADORES TURÍSTICOS E SERVIÇOS DE RESERVAS</t>
+          <t>SELEÇÃO, AGENCIAMENTO E LOCAÇÃO DE MÃO-DE-OBRA</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>2.835991</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>2.525799</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>2.078301</v>
+        <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>2.613853</v>
+        <v>0</v>
       </c>
       <c r="V55" t="n">
-        <v>2.101391</v>
+        <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>1.471389</v>
+        <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>1.273753</v>
+        <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.164082</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>0.845183</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0.5946360000000001</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>0.538106</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>0.517972</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
-        <v>0.562551</v>
+        <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.471001</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>0.239617</v>
-      </c>
-      <c r="AG55" t="n">
-        <v>140</v>
+        <v>0</v>
+      </c>
+      <c r="AG55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>6/12</t>
+          <t>0/12</t>
         </is>
       </c>
     </row>
@@ -6509,24 +6397,24 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ATIVIDADES DE VIGILÂNCIA, SEGURANÇA E INVESTIGAÇÃO</t>
+          <t>AGÊNCIAS DE VIAGENS, OPERADORES TURÍSTICOS E SERVIÇOS DE RESERVAS</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I56" t="n">
         <v>3</v>
@@ -6535,77 +6423,77 @@
         <v>3</v>
       </c>
       <c r="K56" t="n">
+        <v>4</v>
+      </c>
+      <c r="L56" t="n">
         <v>5</v>
       </c>
-      <c r="L56" t="n">
-        <v>7</v>
-      </c>
       <c r="M56" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N56" t="n">
+        <v>5</v>
+      </c>
+      <c r="O56" t="n">
+        <v>6</v>
+      </c>
+      <c r="P56" t="n">
         <v>8</v>
-      </c>
-      <c r="O56" t="n">
-        <v>10</v>
-      </c>
-      <c r="P56" t="n">
-        <v>11</v>
       </c>
       <c r="Q56" t="n">
         <v>12</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>2.835991</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>2.525799</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>2.078301</v>
       </c>
       <c r="U56" t="n">
-        <v>4.771319</v>
+        <v>2.613853</v>
       </c>
       <c r="V56" t="n">
-        <v>4.763152</v>
+        <v>2.101391</v>
       </c>
       <c r="W56" t="n">
-        <v>2.875897</v>
+        <v>1.471389</v>
       </c>
       <c r="X56" t="n">
-        <v>2.712621</v>
+        <v>1.273753</v>
       </c>
       <c r="Y56" t="n">
-        <v>2.707569</v>
+        <v>1.164082</v>
       </c>
       <c r="Z56" t="n">
-        <v>2.02844</v>
+        <v>0.845183</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.662982</v>
+        <v>0.5946360000000001</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.59153</v>
+        <v>0.538106</v>
       </c>
       <c r="AC56" t="n">
-        <v>1.408794</v>
+        <v>0.517972</v>
       </c>
       <c r="AD56" t="n">
-        <v>1.294427</v>
+        <v>0.562551</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.985903</v>
+        <v>1.471001</v>
       </c>
       <c r="AF56" t="n">
         <v>0.239617</v>
       </c>
       <c r="AG56" t="n">
-        <v>50</v>
+        <v>140</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>8/12</t>
+          <t>6/12</t>
         </is>
       </c>
     </row>
@@ -6621,103 +6509,103 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>SERVIÇOS PARA EDIFÍCIOS E ATIVIDADES PAISAGÍSTICAS</t>
+          <t>ATIVIDADES DE VIGILÂNCIA, SEGURANÇA E INVESTIGAÇÃO</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
         <v>2</v>
       </c>
       <c r="I57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K57" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L57" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M57" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N57" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="O57" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="P57" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Q57" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="R57" t="n">
-        <v>0.116129</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>0.110314</v>
+        <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>0.193821</v>
+        <v>0</v>
       </c>
       <c r="U57" t="n">
-        <v>0.171718</v>
+        <v>4.771319</v>
       </c>
       <c r="V57" t="n">
-        <v>0.150852</v>
+        <v>4.763152</v>
       </c>
       <c r="W57" t="n">
-        <v>0.116599</v>
+        <v>2.875897</v>
       </c>
       <c r="X57" t="n">
-        <v>0.088723</v>
+        <v>2.712621</v>
       </c>
       <c r="Y57" t="n">
-        <v>0.07847999999999999</v>
+        <v>2.707569</v>
       </c>
       <c r="Z57" t="n">
-        <v>0.106139</v>
+        <v>2.02844</v>
       </c>
       <c r="AA57" t="n">
-        <v>0.096923</v>
+        <v>1.662982</v>
       </c>
       <c r="AB57" t="n">
-        <v>0.090626</v>
+        <v>1.59153</v>
       </c>
       <c r="AC57" t="n">
-        <v>0.223328</v>
+        <v>1.408794</v>
       </c>
       <c r="AD57" t="n">
-        <v>0.257885</v>
+        <v>1.294427</v>
       </c>
       <c r="AE57" t="n">
-        <v>0.13858</v>
+        <v>1.985903</v>
       </c>
       <c r="AF57" t="n">
-        <v>0.199681</v>
+        <v>0.239617</v>
       </c>
       <c r="AG57" t="n">
-        <v>233.333333</v>
+        <v>50</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>8/12</t>
         </is>
       </c>
     </row>
@@ -6733,439 +6621,439 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE ESCRITÓRIO, DE APOIO ADMINISTRATIVO E OUTROS SERVIÇOS PRESTADOS PRINCIPALMENTE ÀS EMPRESAS</t>
+          <t>SERVIÇOS PARA EDIFÍCIOS E ATIVIDADES PAISAGÍSTICAS</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I58" t="n">
+        <v>2</v>
+      </c>
+      <c r="J58" t="n">
+        <v>2</v>
+      </c>
+      <c r="K58" t="n">
+        <v>2</v>
+      </c>
+      <c r="L58" t="n">
+        <v>2</v>
+      </c>
+      <c r="M58" t="n">
         <v>3</v>
       </c>
-      <c r="J58" t="n">
-        <v>7</v>
-      </c>
-      <c r="K58" t="n">
-        <v>14</v>
-      </c>
-      <c r="L58" t="n">
-        <v>18</v>
-      </c>
-      <c r="M58" t="n">
-        <v>22</v>
-      </c>
       <c r="N58" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="O58" t="n">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="P58" t="n">
-        <v>86</v>
+        <v>8</v>
       </c>
       <c r="Q58" t="n">
-        <v>142</v>
+        <v>10</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>0.116129</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>0.110314</v>
       </c>
       <c r="T58" t="n">
-        <v>0</v>
+        <v>0.193821</v>
       </c>
       <c r="U58" t="n">
-        <v>0.206593</v>
+        <v>0.171718</v>
       </c>
       <c r="V58" t="n">
-        <v>0.465455</v>
+        <v>0.150852</v>
       </c>
       <c r="W58" t="n">
-        <v>0.663503</v>
+        <v>0.116599</v>
       </c>
       <c r="X58" t="n">
-        <v>0.813141</v>
+        <v>0.088723</v>
       </c>
       <c r="Y58" t="n">
-        <v>0.770872</v>
+        <v>0.07847999999999999</v>
       </c>
       <c r="Z58" t="n">
-        <v>0.701539</v>
+        <v>0.106139</v>
       </c>
       <c r="AA58" t="n">
-        <v>0.74766</v>
+        <v>0.096923</v>
       </c>
       <c r="AB58" t="n">
-        <v>0.803401</v>
+        <v>0.090626</v>
       </c>
       <c r="AC58" t="n">
-        <v>0.806226</v>
+        <v>0.223328</v>
       </c>
       <c r="AD58" t="n">
-        <v>0.915083</v>
+        <v>0.257885</v>
       </c>
       <c r="AE58" t="n">
-        <v>0.530267</v>
+        <v>0.13858</v>
       </c>
       <c r="AF58" t="n">
-        <v>2.835463</v>
+        <v>0.199681</v>
       </c>
       <c r="AG58" t="n">
-        <v>305.714286</v>
+        <v>233.333333</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>10/12</t>
+          <t>4/12</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>N</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ADMINISTRAÇÃO PÚBLICA, DEFESA E SEGURIDADE SOCIAL</t>
+          <t>ATIVIDADES ADMINISTRATIVAS E SERVIÇOS COMPLEMENTARES</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ADMINISTRAÇÃO PÚBLICA, DEFESA E SEGURIDADE SOCIAL</t>
+          <t>SERVIÇOS DE ESCRITÓRIO, DE APOIO ADMINISTRATIVO E OUTROS SERVIÇOS PRESTADOS PRINCIPALMENTE ÀS EMPRESAS</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I59" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J59" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K59" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L59" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="M59" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="N59" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="O59" t="n">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="P59" t="n">
-        <v>13</v>
+        <v>86</v>
       </c>
       <c r="Q59" t="n">
-        <v>13</v>
+        <v>142</v>
       </c>
       <c r="R59" t="n">
-        <v>1.19245</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>1.164209</v>
+        <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>1.160428</v>
+        <v>0</v>
       </c>
       <c r="U59" t="n">
-        <v>0.980195</v>
+        <v>0.206593</v>
       </c>
       <c r="V59" t="n">
-        <v>0.939478</v>
+        <v>0.465455</v>
       </c>
       <c r="W59" t="n">
-        <v>0.777508</v>
+        <v>0.663503</v>
       </c>
       <c r="X59" t="n">
-        <v>0.6249209999999999</v>
+        <v>0.813141</v>
       </c>
       <c r="Y59" t="n">
-        <v>0.578357</v>
+        <v>0.770872</v>
       </c>
       <c r="Z59" t="n">
-        <v>0.58804</v>
+        <v>0.701539</v>
       </c>
       <c r="AA59" t="n">
-        <v>0.602522</v>
+        <v>0.74766</v>
       </c>
       <c r="AB59" t="n">
-        <v>0.658192</v>
+        <v>0.803401</v>
       </c>
       <c r="AC59" t="n">
-        <v>0.66723</v>
+        <v>0.806226</v>
       </c>
       <c r="AD59" t="n">
-        <v>0.677959</v>
+        <v>0.915083</v>
       </c>
       <c r="AE59" t="n">
-        <v>0.816268</v>
+        <v>0.530267</v>
       </c>
       <c r="AF59" t="n">
-        <v>0.259585</v>
+        <v>2.835463</v>
       </c>
       <c r="AG59" t="n">
-        <v>8.333333</v>
+        <v>305.714286</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>5/12</t>
+          <t>10/12</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>EDUCAÇÃO</t>
+          <t>ADMINISTRAÇÃO PÚBLICA, DEFESA E SEGURIDADE SOCIAL</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>EDUCAÇÃO</t>
+          <t>ADMINISTRAÇÃO PÚBLICA, DEFESA E SEGURIDADE SOCIAL</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F60" t="n">
+        <v>8</v>
+      </c>
+      <c r="G60" t="n">
         <v>9</v>
       </c>
-      <c r="G60" t="n">
+      <c r="H60" t="n">
+        <v>9</v>
+      </c>
+      <c r="I60" t="n">
+        <v>10</v>
+      </c>
+      <c r="J60" t="n">
+        <v>10</v>
+      </c>
+      <c r="K60" t="n">
+        <v>10</v>
+      </c>
+      <c r="L60" t="n">
+        <v>10</v>
+      </c>
+      <c r="M60" t="n">
         <v>11</v>
       </c>
-      <c r="H60" t="n">
-        <v>14</v>
-      </c>
-      <c r="I60" t="n">
-        <v>16</v>
-      </c>
-      <c r="J60" t="n">
-        <v>21</v>
-      </c>
-      <c r="K60" t="n">
-        <v>36</v>
-      </c>
-      <c r="L60" t="n">
-        <v>41</v>
-      </c>
-      <c r="M60" t="n">
-        <v>49</v>
-      </c>
       <c r="N60" t="n">
-        <v>61</v>
+        <v>12</v>
       </c>
       <c r="O60" t="n">
-        <v>81</v>
+        <v>13</v>
       </c>
       <c r="P60" t="n">
-        <v>102</v>
+        <v>13</v>
       </c>
       <c r="Q60" t="n">
-        <v>135</v>
+        <v>13</v>
       </c>
       <c r="R60" t="n">
-        <v>1.063997</v>
+        <v>1.19245</v>
       </c>
       <c r="S60" t="n">
-        <v>1.145829</v>
+        <v>1.164209</v>
       </c>
       <c r="T60" t="n">
-        <v>1.07395</v>
+        <v>1.160428</v>
       </c>
       <c r="U60" t="n">
-        <v>1.03755</v>
+        <v>0.980195</v>
       </c>
       <c r="V60" t="n">
-        <v>0.855336</v>
+        <v>0.939478</v>
       </c>
       <c r="W60" t="n">
-        <v>0.804155</v>
+        <v>0.777508</v>
       </c>
       <c r="X60" t="n">
-        <v>1.001393</v>
+        <v>0.6249209999999999</v>
       </c>
       <c r="Y60" t="n">
-        <v>0.949407</v>
+        <v>0.578357</v>
       </c>
       <c r="Z60" t="n">
-        <v>0.94811</v>
+        <v>0.58804</v>
       </c>
       <c r="AA60" t="n">
-        <v>0.88536</v>
+        <v>0.602522</v>
       </c>
       <c r="AB60" t="n">
-        <v>0.89234</v>
+        <v>0.658192</v>
       </c>
       <c r="AC60" t="n">
-        <v>0.8269919999999999</v>
+        <v>0.66723</v>
       </c>
       <c r="AD60" t="n">
-        <v>0.802859</v>
+        <v>0.677959</v>
       </c>
       <c r="AE60" t="n">
-        <v>0.945175</v>
+        <v>0.816268</v>
       </c>
       <c r="AF60" t="n">
-        <v>2.695687</v>
+        <v>0.259585</v>
       </c>
       <c r="AG60" t="n">
-        <v>121.311475</v>
+        <v>8.333333</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>12/12</t>
+          <t>5/12</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>P</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SAÚDE HUMANA E SERVIÇOS SOCIAIS</t>
+          <t>EDUCAÇÃO</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ATIVIDADES DE ATENÇÃO À SAÚDE HUMANA</t>
+          <t>EDUCAÇÃO</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F61" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G61" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H61" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I61" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="K61" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="L61" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="M61" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="N61" t="n">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="O61" t="n">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="P61" t="n">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="Q61" t="n">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="R61" t="n">
-        <v>0.7767039999999999</v>
+        <v>1.063997</v>
       </c>
       <c r="S61" t="n">
-        <v>0.829851</v>
+        <v>1.145829</v>
       </c>
       <c r="T61" t="n">
-        <v>1.060144</v>
+        <v>1.07395</v>
       </c>
       <c r="U61" t="n">
-        <v>0.803188</v>
+        <v>1.03755</v>
       </c>
       <c r="V61" t="n">
-        <v>0.891003</v>
+        <v>0.855336</v>
       </c>
       <c r="W61" t="n">
-        <v>0.679477</v>
+        <v>0.804155</v>
       </c>
       <c r="X61" t="n">
-        <v>0.798858</v>
+        <v>1.001393</v>
       </c>
       <c r="Y61" t="n">
-        <v>0.789099</v>
+        <v>0.949407</v>
       </c>
       <c r="Z61" t="n">
-        <v>0.809627</v>
+        <v>0.94811</v>
       </c>
       <c r="AA61" t="n">
-        <v>0.791004</v>
+        <v>0.88536</v>
       </c>
       <c r="AB61" t="n">
-        <v>0.767891</v>
+        <v>0.89234</v>
       </c>
       <c r="AC61" t="n">
-        <v>0.7477009999999999</v>
+        <v>0.8269919999999999</v>
       </c>
       <c r="AD61" t="n">
-        <v>0.807025</v>
+        <v>0.802859</v>
       </c>
       <c r="AE61" t="n">
-        <v>0.811659</v>
+        <v>0.945175</v>
       </c>
       <c r="AF61" t="n">
-        <v>1.976837</v>
+        <v>2.695687</v>
       </c>
       <c r="AG61" t="n">
-        <v>125</v>
+        <v>121.311475</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
-          <t>11/12</t>
+          <t>12/12</t>
         </is>
       </c>
     </row>
@@ -7181,127 +7069,127 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ATIVIDADES DE ATENÇÃO À SAÚDE HUMANA INTEGRADAS COM ASSISTÊNCIA SOCIAL, PRESTADAS EM RESIDÊNCIAS COLETIVAS E PARTICULARES</t>
+          <t>ATIVIDADES DE ATENÇÃO À SAÚDE HUMANA</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F62" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G62" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H62" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I62" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J62" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="K62" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="L62" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="M62" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="N62" t="n">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="O62" t="n">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="P62" t="n">
-        <v>4</v>
+        <v>71</v>
       </c>
       <c r="Q62" t="n">
-        <v>9</v>
+        <v>99</v>
       </c>
       <c r="R62" t="n">
-        <v>1.517855</v>
+        <v>0.7767039999999999</v>
       </c>
       <c r="S62" t="n">
-        <v>1.464963</v>
+        <v>0.829851</v>
       </c>
       <c r="T62" t="n">
-        <v>1.39939</v>
+        <v>1.060144</v>
       </c>
       <c r="U62" t="n">
-        <v>1.252471</v>
+        <v>0.803188</v>
       </c>
       <c r="V62" t="n">
-        <v>2.189955</v>
+        <v>0.891003</v>
       </c>
       <c r="W62" t="n">
-        <v>2.692329</v>
+        <v>0.679477</v>
       </c>
       <c r="X62" t="n">
-        <v>2.112715</v>
+        <v>0.798858</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.700102</v>
+        <v>0.789099</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.422543</v>
+        <v>0.809627</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.15954</v>
+        <v>0.791004</v>
       </c>
       <c r="AB62" t="n">
-        <v>0.841155</v>
+        <v>0.767891</v>
       </c>
       <c r="AC62" t="n">
-        <v>0.741134</v>
+        <v>0.7477009999999999</v>
       </c>
       <c r="AD62" t="n">
-        <v>0.899239</v>
+        <v>0.807025</v>
       </c>
       <c r="AE62" t="n">
-        <v>1.491799</v>
+        <v>0.811659</v>
       </c>
       <c r="AF62" t="n">
-        <v>0.179712</v>
+        <v>1.976837</v>
       </c>
       <c r="AG62" t="n">
-        <v>200</v>
+        <v>125</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>11/12</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ARTES, CULTURA, ESPORTE E RECREAÇÃO</t>
+          <t>SAÚDE HUMANA E SERVIÇOS SOCIAIS</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ATIVIDADES ARTÍSTICAS, CRIATIVAS E DE ESPETÁCULOS</t>
+          <t>ATIVIDADES DE ATENÇÃO À SAÚDE HUMANA INTEGRADAS COM ASSISTÊNCIA SOCIAL, PRESTADAS EM RESIDÊNCIAS COLETIVAS E PARTICULARES</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F63" t="n">
         <v>1</v>
@@ -7313,83 +7201,83 @@
         <v>1</v>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N63" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O63" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="P63" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="Q63" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>1.517855</v>
       </c>
       <c r="S63" t="n">
-        <v>1.831204</v>
+        <v>1.464963</v>
       </c>
       <c r="T63" t="n">
-        <v>1.457698</v>
+        <v>1.39939</v>
       </c>
       <c r="U63" t="n">
-        <v>1.178797</v>
+        <v>1.252471</v>
       </c>
       <c r="V63" t="n">
-        <v>0.992323</v>
+        <v>2.189955</v>
       </c>
       <c r="W63" t="n">
-        <v>0.6489200000000001</v>
+        <v>2.692329</v>
       </c>
       <c r="X63" t="n">
-        <v>0.402422</v>
+        <v>2.112715</v>
       </c>
       <c r="Y63" t="n">
-        <v>0.291252</v>
+        <v>1.700102</v>
       </c>
       <c r="Z63" t="n">
-        <v>0.417279</v>
+        <v>1.422543</v>
       </c>
       <c r="AA63" t="n">
-        <v>0.849739</v>
+        <v>1.15954</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.046016</v>
+        <v>0.841155</v>
       </c>
       <c r="AC63" t="n">
-        <v>1.046775</v>
+        <v>0.741134</v>
       </c>
       <c r="AD63" t="n">
-        <v>0.864672</v>
+        <v>0.899239</v>
       </c>
       <c r="AE63" t="n">
-        <v>0.848238</v>
+        <v>1.491799</v>
       </c>
       <c r="AF63" t="n">
-        <v>0.399361</v>
+        <v>0.179712</v>
       </c>
       <c r="AG63" t="n">
-        <v>233.333333</v>
+        <v>200</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>6/12</t>
+          <t>4/12</t>
         </is>
       </c>
     </row>
@@ -7405,105 +7293,103 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ATIVIDADES DE EXPLORAÇÃO DE JOGOS DE AZAR E APOSTAS</t>
+          <t>ATIVIDADES ARTÍSTICAS, CRIATIVAS E DE ESPETÁCULOS</t>
         </is>
       </c>
       <c r="E64" t="n">
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q64" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>0</v>
+        <v>1.831204</v>
       </c>
       <c r="T64" t="n">
-        <v>0</v>
+        <v>1.457698</v>
       </c>
       <c r="U64" t="n">
-        <v>0</v>
+        <v>1.178797</v>
       </c>
       <c r="V64" t="n">
-        <v>0</v>
+        <v>0.992323</v>
       </c>
       <c r="W64" t="n">
-        <v>0</v>
+        <v>0.6489200000000001</v>
       </c>
       <c r="X64" t="n">
-        <v>0</v>
+        <v>0.402422</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>0.291252</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>0.417279</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>0.849739</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.046016</v>
       </c>
       <c r="AC64" t="n">
-        <v>0</v>
+        <v>1.046775</v>
       </c>
       <c r="AD64" t="n">
-        <v>7.88424</v>
+        <v>0.864672</v>
       </c>
       <c r="AE64" t="n">
-        <v>0.60648</v>
+        <v>0.848238</v>
       </c>
       <c r="AF64" t="n">
-        <v>0.019968</v>
-      </c>
-      <c r="AG64" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.399361</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>233.333333</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>6/12</t>
         </is>
       </c>
     </row>
@@ -7519,215 +7405,217 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ATIVIDADES ESPORTIVAS E DE RECREAÇÃO E LAZER</t>
+          <t>ATIVIDADES DE EXPLORAÇÃO DE JOGOS DE AZAR E APOSTAS</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="R65" t="n">
-        <v>0.918475</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>0.8495279999999999</v>
+        <v>0</v>
       </c>
       <c r="T65" t="n">
-        <v>0.73566</v>
+        <v>0</v>
       </c>
       <c r="U65" t="n">
-        <v>0.624934</v>
+        <v>0</v>
       </c>
       <c r="V65" t="n">
-        <v>0.691565</v>
+        <v>0</v>
       </c>
       <c r="W65" t="n">
-        <v>0.522351</v>
+        <v>0</v>
       </c>
       <c r="X65" t="n">
-        <v>0.550683</v>
+        <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>0.523778</v>
+        <v>0</v>
       </c>
       <c r="Z65" t="n">
-        <v>0.6733130000000001</v>
+        <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>0.69125</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>0.666162</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
-        <v>0.863677</v>
+        <v>0</v>
       </c>
       <c r="AD65" t="n">
-        <v>1.001462</v>
+        <v>7.88424</v>
       </c>
       <c r="AE65" t="n">
-        <v>0.716372</v>
+        <v>0.60648</v>
       </c>
       <c r="AF65" t="n">
-        <v>0.798722</v>
-      </c>
-      <c r="AG65" t="n">
-        <v>185.714286</v>
+        <v>0.019968</v>
+      </c>
+      <c r="AG65" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>8/12</t>
+          <t>1/12</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>R</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>OUTRAS ATIVIDADES DE SERVIÇOS</t>
+          <t>ARTES, CULTURA, ESPORTE E RECREAÇÃO</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ATIVIDADES DE ORGANIZAÇÕES ASSOCIATIVAS</t>
+          <t>ATIVIDADES ESPORTIVAS E DE RECREAÇÃO E LAZER</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>63</v>
+        <v>3</v>
       </c>
       <c r="F66" t="n">
-        <v>69</v>
+        <v>3</v>
       </c>
       <c r="G66" t="n">
-        <v>84</v>
+        <v>3</v>
       </c>
       <c r="H66" t="n">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="I66" t="n">
-        <v>123</v>
+        <v>4</v>
       </c>
       <c r="J66" t="n">
-        <v>147</v>
+        <v>4</v>
       </c>
       <c r="K66" t="n">
-        <v>156</v>
+        <v>6</v>
       </c>
       <c r="L66" t="n">
-        <v>167</v>
+        <v>7</v>
       </c>
       <c r="M66" t="n">
-        <v>177</v>
+        <v>11</v>
       </c>
       <c r="N66" t="n">
-        <v>183</v>
+        <v>14</v>
       </c>
       <c r="O66" t="n">
-        <v>191</v>
+        <v>17</v>
       </c>
       <c r="P66" t="n">
-        <v>197</v>
+        <v>28</v>
       </c>
       <c r="Q66" t="n">
-        <v>204</v>
+        <v>40</v>
       </c>
       <c r="R66" t="n">
-        <v>1.220889</v>
+        <v>0.918475</v>
       </c>
       <c r="S66" t="n">
-        <v>1.179217</v>
+        <v>0.8495279999999999</v>
       </c>
       <c r="T66" t="n">
-        <v>1.124223</v>
+        <v>0.73566</v>
       </c>
       <c r="U66" t="n">
-        <v>1.111086</v>
+        <v>0.624934</v>
       </c>
       <c r="V66" t="n">
-        <v>1.131565</v>
+        <v>0.691565</v>
       </c>
       <c r="W66" t="n">
-        <v>1.010995</v>
+        <v>0.522351</v>
       </c>
       <c r="X66" t="n">
-        <v>0.843713</v>
+        <v>0.550683</v>
       </c>
       <c r="Y66" t="n">
-        <v>0.824504</v>
+        <v>0.523778</v>
       </c>
       <c r="Z66" t="n">
-        <v>0.806969</v>
+        <v>0.6733130000000001</v>
       </c>
       <c r="AA66" t="n">
-        <v>0.80022</v>
+        <v>0.69125</v>
       </c>
       <c r="AB66" t="n">
-        <v>0.815925</v>
+        <v>0.666162</v>
       </c>
       <c r="AC66" t="n">
-        <v>0.8243819999999999</v>
+        <v>0.863677</v>
       </c>
       <c r="AD66" t="n">
-        <v>0.83391</v>
+        <v>1.001462</v>
       </c>
       <c r="AE66" t="n">
-        <v>0.963661</v>
+        <v>0.716372</v>
       </c>
       <c r="AF66" t="n">
-        <v>4.073482</v>
+        <v>0.798722</v>
       </c>
       <c r="AG66" t="n">
-        <v>11.47541</v>
+        <v>185.714286</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>12/12</t>
+          <t>8/12</t>
         </is>
       </c>
     </row>
@@ -7743,103 +7631,103 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>REPARAÇÃO E MANUTENÇÃO DE EQUIPAMENTOS DE INFORMÁTICA E COMUNICAÇÃO E DE OBJETOS PESSOAIS E DOMÉSTICOS</t>
+          <t>ATIVIDADES DE ORGANIZAÇÕES ASSOCIATIVAS</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="F67" t="n">
-        <v>1</v>
+        <v>69</v>
       </c>
       <c r="G67" t="n">
-        <v>1</v>
+        <v>84</v>
       </c>
       <c r="H67" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="I67" t="n">
-        <v>2</v>
+        <v>123</v>
       </c>
       <c r="J67" t="n">
-        <v>6</v>
+        <v>147</v>
       </c>
       <c r="K67" t="n">
-        <v>9</v>
+        <v>156</v>
       </c>
       <c r="L67" t="n">
-        <v>12</v>
+        <v>167</v>
       </c>
       <c r="M67" t="n">
-        <v>16</v>
+        <v>177</v>
       </c>
       <c r="N67" t="n">
-        <v>24</v>
+        <v>183</v>
       </c>
       <c r="O67" t="n">
-        <v>34</v>
+        <v>191</v>
       </c>
       <c r="P67" t="n">
-        <v>44</v>
+        <v>197</v>
       </c>
       <c r="Q67" t="n">
-        <v>62</v>
+        <v>204</v>
       </c>
       <c r="R67" t="n">
-        <v>1.088562</v>
+        <v>1.220889</v>
       </c>
       <c r="S67" t="n">
-        <v>0.963792</v>
+        <v>1.179217</v>
       </c>
       <c r="T67" t="n">
-        <v>0.795108</v>
+        <v>1.124223</v>
       </c>
       <c r="U67" t="n">
-        <v>1.327122</v>
+        <v>1.111086</v>
       </c>
       <c r="V67" t="n">
-        <v>1.018856</v>
+        <v>1.131565</v>
       </c>
       <c r="W67" t="n">
-        <v>1.035088</v>
+        <v>1.010995</v>
       </c>
       <c r="X67" t="n">
-        <v>0.868468</v>
+        <v>0.843713</v>
       </c>
       <c r="Y67" t="n">
-        <v>0.834684</v>
+        <v>0.824504</v>
       </c>
       <c r="Z67" t="n">
-        <v>0.825128</v>
+        <v>0.806969</v>
       </c>
       <c r="AA67" t="n">
-        <v>0.839724</v>
+        <v>0.80022</v>
       </c>
       <c r="AB67" t="n">
-        <v>0.847454</v>
+        <v>0.815925</v>
       </c>
       <c r="AC67" t="n">
-        <v>0.84178</v>
+        <v>0.8243819999999999</v>
       </c>
       <c r="AD67" t="n">
-        <v>0.902039</v>
+        <v>0.83391</v>
       </c>
       <c r="AE67" t="n">
-        <v>0.937523</v>
+        <v>0.963661</v>
       </c>
       <c r="AF67" t="n">
-        <v>1.238019</v>
+        <v>4.073482</v>
       </c>
       <c r="AG67" t="n">
-        <v>158.333333</v>
+        <v>11.47541</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>9/12</t>
+          <t>12/12</t>
         </is>
       </c>
     </row>
@@ -7855,11 +7743,11 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>OUTRAS ATIVIDADES DE SERVIÇOS PESSOAIS</t>
+          <t>REPARAÇÃO E MANUTENÇÃO DE EQUIPAMENTOS DE INFORMÁTICA E COMUNICAÇÃO E DE OBJETOS PESSOAIS E DOMÉSTICOS</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -7872,82 +7760,82 @@
         <v>1</v>
       </c>
       <c r="H68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I68" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J68" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K68" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="L68" t="n">
+        <v>12</v>
+      </c>
+      <c r="M68" t="n">
+        <v>16</v>
+      </c>
+      <c r="N68" t="n">
+        <v>24</v>
+      </c>
+      <c r="O68" t="n">
+        <v>34</v>
+      </c>
+      <c r="P68" t="n">
         <v>44</v>
       </c>
-      <c r="M68" t="n">
-        <v>59</v>
-      </c>
-      <c r="N68" t="n">
-        <v>87</v>
-      </c>
-      <c r="O68" t="n">
-        <v>132</v>
-      </c>
-      <c r="P68" t="n">
-        <v>179</v>
-      </c>
       <c r="Q68" t="n">
-        <v>235</v>
+        <v>62</v>
       </c>
       <c r="R68" t="n">
-        <v>0.822654</v>
+        <v>1.088562</v>
       </c>
       <c r="S68" t="n">
-        <v>0.682436</v>
+        <v>0.963792</v>
       </c>
       <c r="T68" t="n">
-        <v>0.546637</v>
+        <v>0.795108</v>
       </c>
       <c r="U68" t="n">
-        <v>0.428195</v>
+        <v>1.327122</v>
       </c>
       <c r="V68" t="n">
-        <v>1.346474</v>
+        <v>1.018856</v>
       </c>
       <c r="W68" t="n">
         <v>1.035088</v>
       </c>
       <c r="X68" t="n">
-        <v>1.319213</v>
+        <v>0.868468</v>
       </c>
       <c r="Y68" t="n">
-        <v>1.370512</v>
+        <v>0.834684</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.271667</v>
+        <v>0.825128</v>
       </c>
       <c r="AA68" t="n">
-        <v>1.155183</v>
+        <v>0.839724</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.128329</v>
+        <v>0.847454</v>
       </c>
       <c r="AC68" t="n">
-        <v>1.081812</v>
+        <v>0.84178</v>
       </c>
       <c r="AD68" t="n">
-        <v>1.041908</v>
+        <v>0.902039</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.017701</v>
+        <v>0.937523</v>
       </c>
       <c r="AF68" t="n">
-        <v>4.692492</v>
+        <v>1.238019</v>
       </c>
       <c r="AG68" t="n">
-        <v>170.114943</v>
+        <v>158.333333</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -7958,234 +7846,346 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SERVIÇOS DOMÉSTICOS</t>
+          <t>OUTRAS ATIVIDADES DE SERVIÇOS</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>SERVIÇOS DOMÉSTICOS</t>
+          <t>OUTRAS ATIVIDADES DE SERVIÇOS PESSOAIS</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J69" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K69" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="L69" t="n">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="M69" t="n">
-        <v>5</v>
+        <v>59</v>
       </c>
       <c r="N69" t="n">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="O69" t="n">
-        <v>12</v>
+        <v>132</v>
       </c>
       <c r="P69" t="n">
-        <v>16</v>
+        <v>179</v>
       </c>
       <c r="Q69" t="n">
-        <v>22</v>
-      </c>
-      <c r="R69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>235</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0.822654</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0.682436</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0.546637</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0.428195</v>
+      </c>
+      <c r="V69" t="n">
+        <v>1.346474</v>
       </c>
       <c r="W69" t="n">
-        <v>21.089912</v>
+        <v>1.035088</v>
       </c>
       <c r="X69" t="n">
-        <v>9.155097</v>
+        <v>1.319213</v>
       </c>
       <c r="Y69" t="n">
-        <v>5.041681</v>
+        <v>1.370512</v>
       </c>
       <c r="Z69" t="n">
-        <v>4.621763</v>
+        <v>1.271667</v>
       </c>
       <c r="AA69" t="n">
-        <v>3.655693</v>
+        <v>1.155183</v>
       </c>
       <c r="AB69" t="n">
-        <v>2.371501</v>
+        <v>1.128329</v>
       </c>
       <c r="AC69" t="n">
-        <v>1.942586</v>
+        <v>1.081812</v>
       </c>
       <c r="AD69" t="n">
-        <v>1.87241</v>
+        <v>1.041908</v>
       </c>
       <c r="AE69" t="n">
-        <v>6.218831</v>
+        <v>1.017701</v>
       </c>
       <c r="AF69" t="n">
-        <v>0.439297</v>
+        <v>4.692492</v>
       </c>
       <c r="AG69" t="n">
-        <v>120</v>
+        <v>170.114943</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>7/12</t>
+          <t>9/12</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>SERVIÇOS DOMÉSTICOS</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>97</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>SERVIÇOS DOMÉSTICOS</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>1</v>
+      </c>
+      <c r="K70" t="n">
+        <v>1</v>
+      </c>
+      <c r="L70" t="n">
+        <v>2</v>
+      </c>
+      <c r="M70" t="n">
+        <v>5</v>
+      </c>
+      <c r="N70" t="n">
+        <v>10</v>
+      </c>
+      <c r="O70" t="n">
+        <v>12</v>
+      </c>
+      <c r="P70" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>22</v>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W70" t="n">
+        <v>21.089912</v>
+      </c>
+      <c r="X70" t="n">
+        <v>9.155097</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>5.041681</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>4.621763</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>3.655693</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>2.371501</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>1.942586</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>1.87241</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>6.218831</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>0.439297</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>120</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>7/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
           <t>U</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>ORGANISMOS INTERNACIONAIS E OUTRAS INSTITUIÇÕES EXTRATERRITORIAIS</t>
         </is>
       </c>
-      <c r="C70" t="n">
+      <c r="C71" t="n">
         <v>99</v>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>ORGANISMOS INTERNACIONAIS E OUTRAS INSTITUIÇÕES EXTRATERRITORIAIS</t>
         </is>
       </c>
-      <c r="E70" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" t="n">
-        <v>0</v>
-      </c>
-      <c r="M70" t="n">
-        <v>0</v>
-      </c>
-      <c r="N70" t="n">
-        <v>0</v>
-      </c>
-      <c r="O70" t="n">
-        <v>0</v>
-      </c>
-      <c r="P70" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
-      <c r="R70" t="n">
-        <v>0</v>
-      </c>
-      <c r="S70" t="n">
-        <v>0</v>
-      </c>
-      <c r="T70" t="n">
-        <v>0</v>
-      </c>
-      <c r="U70" t="n">
-        <v>0</v>
-      </c>
-      <c r="V70" t="n">
-        <v>0</v>
-      </c>
-      <c r="W70" t="n">
-        <v>0</v>
-      </c>
-      <c r="X70" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y70" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG70" t="inlineStr">
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
+      </c>
+      <c r="V71" t="n">
+        <v>0</v>
+      </c>
+      <c r="W71" t="n">
+        <v>0</v>
+      </c>
+      <c r="X71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AH70" t="inlineStr">
+      <c r="AH71" t="inlineStr">
         <is>
           <t>0/12</t>
         </is>
